--- a/docs/요구사항_정의서_파이온_최종.xlsx
+++ b/docs/요구사항_정의서_파이온_최종.xlsx
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1761,6 +1761,80 @@
       <c r="G15" s="27" t="inlineStr">
         <is>
           <t>문서 대조 CH-04 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-011 화면 출처 표기 요구사항 존재</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-011 삭제, 관련 문장 제거</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 화면 출처 표기를 하지 않기로 함</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="inlineStr">
+        <is>
+          <t>LLM 생성 추천의 출처 표기(REQ-RECO-001)는 안전 조항이라 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>v1.6</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>REQ-RECO-001·NFR-SAFE-005 수용기준에 출처 표기 남아 있음</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>출처 표기 문구 전부 제거</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 화면 출처 표기 전면 제외</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="inlineStr">
+        <is>
+          <t>요구사항 자체는 유지</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.00500011" customWidth="1" min="1" max="1"/>
@@ -4407,6 +4481,90 @@
         </is>
       </c>
       <c r="F82" s="27" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+      <c r="B83" s="27" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-011</t>
+        </is>
+      </c>
+      <c r="C83" s="27" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D83" s="27" t="inlineStr">
+        <is>
+          <t>챌린지 선택 화면의 근거 출처 표기</t>
+        </is>
+      </c>
+      <c r="E83" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 출처 표기 없앰</t>
+        </is>
+      </c>
+      <c r="F83" s="27" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B84" s="27" t="inlineStr">
+        <is>
+          <t>REQ-RECO-001</t>
+        </is>
+      </c>
+      <c r="C84" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D84" s="27" t="inlineStr">
+        <is>
+          <t>출처 표기 문구 제거</t>
+        </is>
+      </c>
+      <c r="E84" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 출처 표기 전면 제외</t>
+        </is>
+      </c>
+      <c r="F84" s="27" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B85" s="27" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-005</t>
+        </is>
+      </c>
+      <c r="C85" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D85" s="27" t="inlineStr">
+        <is>
+          <t>출처 표기 문구 제거</t>
+        </is>
+      </c>
+      <c r="E85" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 출처 표기 전면 제외</t>
+        </is>
+      </c>
+      <c r="F85" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4420,7 +4578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.00500011" customWidth="1" min="1" max="1"/>
@@ -6547,114 +6705,114 @@
       </c>
     </row>
     <row r="38" ht="27" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>REQ-CHAL-011</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>챌린지</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>근거</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>출처 표기</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>신뢰성</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>챌린지 선택 화면에서 각 카테고리와 챌린지의 근거 출처를 함께 표시해야 한다.</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>REQ-DASH-001</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>핵심 지표</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>단일 표시</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>사용자는 대시보드에서 최신 위험도와, 고혈압과 가장 연관된 검진 지표 하나만 확인할 수 있어야 한다. 나머지 지표는 건강정보 화면에서 확인한다.</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>출처는 화면 우측에 배치한다. 대시보드에는 표시하지 않는다. 근거가 없는 항목은 그 사실을 함께 밝힌다.</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>W09 챌린지 선택</t>
-        </is>
-      </c>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>대시보드에 표시하는 검진 지표는 1개(혈압). 측정 기준일과 면책 문구를 함께 표시. 위험 구간은 정상·경계·위험 3단계를 색상과 텍스트로 함께 제시한다(NFR-ACC-003).</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>W08 대시보드 (홈)</t>
+        </is>
+      </c>
+      <c r="K38" s="11" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40.5" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>REQ-DASH-001</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>REQ-DASH-002</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>대시보드</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>요약</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>핵심 지표</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>단일 표시</t>
-        </is>
-      </c>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>사용자는 대시보드에서 최신 위험도와, 고혈압과 가장 연관된 검진 지표 하나만 확인할 수 있어야 한다. 나머지 지표는 건강정보 화면에서 확인한다.</t>
-        </is>
-      </c>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>추이</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>예측 이력</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>차트</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>사용자는 과거 예측 결과의 변화 추이를 차트로 확인할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>대시보드에 표시하는 검진 지표는 1개(혈압). 측정 기준일과 면책 문구를 함께 표시. 위험 구간은 정상·경계·위험 3단계를 색상과 텍스트로 함께 제시한다(NFR-ACC-003).</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>W08 대시보드 (홈)</t>
-        </is>
-      </c>
-      <c r="K39" s="11" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>최소 2건 이상 이력이 있을 때 추이를 표시. 1건 이하는 빈 상태 안내.</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>W11 추이 · 변화 추적</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -6663,7 +6821,7 @@
     <row r="40" ht="27" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>REQ-DASH-002</t>
+          <t>REQ-DASH-003</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -6673,22 +6831,22 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>추이</t>
+          <t>변화</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>예측 이력</t>
+          <t>최초 대비</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>차트</t>
+          <t>증감 표시</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>사용자는 과거 예측 결과의 변화 추이를 차트로 확인할 수 있어야 한다.</t>
+          <t>사용자는 최초 측정 대비 현재 위험도 변화를 확인할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -6698,12 +6856,12 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>최소 2건 이상 이력이 있을 때 추이를 표시. 1건 이하는 빈 상태 안내.</t>
+          <t>증감은 색상 외 기호·텍스트로도 구분(NFR-ACC-003 연계).</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
@@ -6720,7 +6878,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>REQ-DASH-003</t>
+          <t>REQ-DASH-004</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -6730,22 +6888,22 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>변화</t>
+          <t>챌린지</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>최초 대비</t>
+          <t>수행 현황</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>증감 표시</t>
+          <t>통합 보기</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>사용자는 최초 측정 대비 현재 위험도 변화를 확인할 수 있어야 한다.</t>
+          <t>사용자는 위험도 추이와 챌린지 수행 현황을 한 화면에서 확인할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -6755,17 +6913,17 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>증감은 색상 외 기호·텍스트로도 구분(NFR-ACC-003 연계).</t>
+          <t>동일 기간 축으로 정렬하여 표시.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>W11 추이 · 변화 추적</t>
+          <t>W08 대시보드 (홈)</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -6777,7 +6935,7 @@
     <row r="42" ht="27" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>REQ-DASH-004</t>
+          <t>REQ-DASH-005</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -6787,22 +6945,22 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>챌린지</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>수행 현황</t>
+          <t>빈 데이터</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>통합 보기</t>
+          <t>다음 행동</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>사용자는 위험도 추이와 챌린지 수행 현황을 한 화면에서 확인할 수 있어야 한다.</t>
+          <t>데이터가 없는 사용자는 빈 상태 안내와 다음 행동을 확인할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -6812,134 +6970,134 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>빈 화면 대신 건강정보 입력 유도 CTA를 표시.</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>W08 대시보드 (홈)</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="27" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>REQ-DASH-006</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>주 행동</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>단일 CTA</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>상태별 전환</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>대시보드는 사용자 상태에 따라 다음 행동 한 가지만 주 버튼으로 노출해야 한다.</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>동일 기간 축으로 정렬하여 표시.</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>건강정보 미입력은 입력, 사이클 진행 중은 오늘 인증, 사이클 종료는 전·후 비교로 전환한다. 한 화면에 주 버튼은 1개. 상태마다 CTA 보조 문구와 미노출 정보를 함께 정의한다 — 입력 전에는 위험도·챌린지·혈압 추이를 숨기고, 진행 중에는 4주 결과를 숨긴다. (PRD Screen Flow)</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
         <is>
           <t>W08 대시보드 (홈)</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K43" s="19" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="27" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>REQ-DASH-005</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
+    <row r="44" ht="27" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>REQ-DASH-007</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>대시보드</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>빈 데이터</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>다음 행동</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>데이터가 없는 사용자는 빈 상태 안내와 다음 행동을 확인할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>검진 지표</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>빈값 표시</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>대시보드에 표시하는 검진 지표는 1개로 하고, 값이 없으면 자리표시자와 입력 경로를 함께 보여준다. 나머지 지표는 건강정보 화면에서 확인한다.</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>빈 화면 대신 건강정보 입력 유도 CTA를 표시.</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>미입력 항목은 자리표시자("—")와 입력 진입점을 함께 표시. 0 또는 공백 표시 금지.</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>W08 대시보드 (홈)</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="27" customHeight="1">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t>REQ-DASH-006</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="inlineStr">
-        <is>
-          <t>대시보드</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="inlineStr">
-        <is>
-          <t>주 행동</t>
-        </is>
-      </c>
-      <c r="D44" s="19" t="inlineStr">
-        <is>
-          <t>단일 CTA</t>
-        </is>
-      </c>
-      <c r="E44" s="19" t="inlineStr">
-        <is>
-          <t>상태별 전환</t>
-        </is>
-      </c>
-      <c r="F44" s="19" t="inlineStr">
-        <is>
-          <t>대시보드는 사용자 상태에 따라 다음 행동 한 가지만 주 버튼으로 노출해야 한다.</t>
-        </is>
-      </c>
-      <c r="G44" s="19" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H44" s="19" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="I44" s="19" t="inlineStr">
-        <is>
-          <t>건강정보 미입력은 입력, 사이클 진행 중은 오늘 인증, 사이클 종료는 전·후 비교로 전환한다. 한 화면에 주 버튼은 1개. 상태마다 CTA 보조 문구와 미노출 정보를 함께 정의한다 — 입력 전에는 위험도·챌린지·혈압 추이를 숨기고, 진행 중에는 4주 결과를 숨긴다. (PRD Screen Flow)</t>
-        </is>
-      </c>
-      <c r="J44" s="19" t="inlineStr">
-        <is>
-          <t>W08 대시보드 (홈)</t>
-        </is>
-      </c>
-      <c r="K44" s="19" t="inlineStr">
+      <c r="K44" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -6948,7 +7106,7 @@
     <row r="45" ht="27" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>REQ-DASH-007</t>
+          <t>REQ-DASH-008</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -6958,22 +7116,22 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>요약</t>
+          <t>챌린지</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>검진 지표</t>
+          <t>진행률</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>빈값 표시</t>
+          <t>현재·목표 병기</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>대시보드에 표시하는 검진 지표는 1개로 하고, 값이 없으면 자리표시자와 입력 경로를 함께 보여준다. 나머지 지표는 건강정보 화면에서 확인한다.</t>
+          <t>챌린지 진행률은 진행 막대와 "현재 / 목표" 수치를 함께 표시해야 한다.</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -6983,17 +7141,17 @@
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>미입력 항목은 자리표시자("—")와 입력 진입점을 함께 표시. 0 또는 공백 표시 금지.</t>
+          <t>막대만 표시 금지. 예) "3 / 5일" 텍스트를 함께 노출.</t>
         </is>
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>W08 대시보드 (홈)</t>
+          <t>W08 대시보드 (홈), W10 챌린지 수행 · 인증</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr">
@@ -7005,7 +7163,7 @@
     <row r="46" ht="27" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>REQ-DASH-008</t>
+          <t>REQ-DASH-009</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -7020,17 +7178,17 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>진행률</t>
+          <t>인증 스트릭</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>현재·목표 병기</t>
+          <t>요일별 표시</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>챌린지 진행률은 진행 막대와 "현재 / 목표" 수치를 함께 표시해야 한다.</t>
+          <t>주간 인증 현황을 요일별 표식으로 표시하고 연속 기록일을 함께 보여준다.</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -7045,7 +7203,7 @@
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>막대만 표시 금지. 예) "3 / 5일" 텍스트를 함께 노출.</t>
+          <t>인증·미인증·오늘을 색상 외 기호로도 구분(NFR-ACC-003 연계).</t>
         </is>
       </c>
       <c r="J46" s="9" t="inlineStr">
@@ -7060,456 +7218,456 @@
       </c>
     </row>
     <row r="47" ht="27" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>REQ-DASH-009</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>REQ-DASH-010</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>대시보드</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>추이</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>기준선 표시</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>혈압 추이 차트에 고혈압 기준선(수축기 140mmHg)을 함께 표시해 구간 이동을 확인할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H47" s="23" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I47" s="23" t="inlineStr">
+        <is>
+          <t>기준선에 수치 라벨을 표기. 구간은 색상 외 텍스트를 병기(NFR-ACC-003).</t>
+        </is>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>W08 대시보드 (홈), W11 추이 · 변화 추적</t>
+        </is>
+      </c>
+      <c r="K47" s="23" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40.5" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>REQ-DASH-011</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>재평가</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>시점</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>안내</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>챌린지 사이클(4주)이 끝나면 생활습관 재설문과 혈압 중심의 중간 피드백을 안내하고, 전체 검진값 재입력은 3~6개월 주기로 따로 안내해야 한다.</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>4주 종료 시 주 버튼은 중간 재평가로 전환한다. 전체 재입력 안내는 마지막 전체 입력일로부터 3개월이 지난 뒤 노출한다.</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>W08 대시보드 (홈)</t>
+        </is>
+      </c>
+      <c r="K48" s="11" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="27" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>NFR-DASH-001</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>동기</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>보상</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>MVP 범위</t>
+        </is>
+      </c>
+      <c r="F49" s="19" t="inlineStr">
+        <is>
+          <t>MVP 단계의 대시보드는 포인트·쿠폰 등 외재적 보상 없이 위험도·혈압 변화와 주간 달성률만으로 동기를 제시한다.</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H49" s="19" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I49" s="19" t="inlineStr">
+        <is>
+          <t>리워드 UI 미존재. 유지율 추이를 확인한 뒤 소셜·리워드 요소를 단계적으로 재검토하며, 재검토 시점과 기준을 문서로 남긴다. 개인 인증률·연속 수행일 기반 배지·포인트는 Phase 2 후보로 두며, 재원과 부정 인증 방지 정책을 먼저 정한다. (PRD CH-08)</t>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>W08 대시보드 (홈), W09 챌린지 선택, W10 챌린지 수행 · 인증</t>
+        </is>
+      </c>
+      <c r="K49" s="19" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40.5" customHeight="1">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>REQ-RECO-001</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>LLM 생성</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>근거 기반</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="inlineStr">
+        <is>
+          <t>행동 제안</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>사용자는 예측 결과와 승인된 건강정보를 근거로 생성된 예방 행동 제안을 확인할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H50" s="23" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I50" s="23" t="inlineStr">
+        <is>
+          <t>제안마다 생성 시각을 표시. 약물·처방 관련 제안 금지.</t>
+        </is>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>W06 예측 결과 · XAI 설명</t>
+        </is>
+      </c>
+      <c r="K50" s="23" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="27" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>REQ-RECO-002</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>추천</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>식단 분석</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>나트륨 점수화</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>이미지 인식</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>사용자는 식단 사진을 올려 나트륨 중심의 점수와 개선 제안을 확인할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>점수 기준은 칼로리가 아닌 나트륨. 음식별 영양소는 식약처 공개 데이터를 기준으로 한다. 분석 실패 시 직접 입력으로 대체 가능.</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>W10 챌린지 수행 · 인증</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="27" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>REQ-NOTI-001</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>리마인더</t>
+        </is>
+      </c>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>시작 알림</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>발송 시각</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="inlineStr">
+        <is>
+          <t>사용자는 아침 지정 시각에 그날의 챌린지 시작 알림을 받을 수 있어야 한다. 문구는 참여를 강요하지 않는 톤으로 한다.</t>
+        </is>
+      </c>
+      <c r="G52" s="19" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H52" s="19" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I52" s="19" t="inlineStr">
+        <is>
+          <t>사용자별 수신 설정을 따르며 미설정 시 발송하지 않는다. 발송 시각은 사용자가 바꿀 수 있다. 웹 푸시는 HTTPS와 사용자 동작으로 받은 권한이 있을 때만 발송한다. 알림 설정과 개인정보 안내를 같은 화면에서 확인할 수 있게 한다. (PRD CH-09)</t>
+        </is>
+      </c>
+      <c r="J52" s="19" t="inlineStr">
+        <is>
+          <t>W12 피드백 · 마이페이지</t>
+        </is>
+      </c>
+      <c r="K52" s="19" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40.5" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>REQ-FEED-001</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>결과·추천</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>의견 수집</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>사용자는 예측 결과와 추천에 대한 평가와 의견을 남길 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>평가 대상(예측/추천)과 대상 버전을 함께 저장.</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>W12 피드백 · 마이페이지</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>REQ-FEED-002</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>챌린지</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>인증 스트릭</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>요일별 표시</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>주간 인증 현황을 요일별 표식으로 표시하고 연속 기록일을 함께 보여준다.</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>난이도</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>사이클 종료 평가</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>사용자는 사이클 종료 시 수행한 챌린지의 난이도를 평가할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H47" s="9" t="inlineStr">
+      <c r="H54" s="9" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>인증·미인증·오늘을 색상 외 기호로도 구분(NFR-ACC-003 연계).</t>
-        </is>
-      </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>W08 대시보드 (홈), W10 챌린지 수행 · 인증</t>
-        </is>
-      </c>
-      <c r="K47" s="9" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="40.5" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>REQ-DASH-010</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>대시보드</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>추이</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>기준선 표시</t>
-        </is>
-      </c>
-      <c r="F48" s="9" t="inlineStr">
-        <is>
-          <t>혈압 추이 차트에 고혈압 기준선(수축기 140mmHg)을 함께 표시해 구간 이동을 확인할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G48" s="9" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>기준선에 수치 라벨을 표기. 구간은 색상 외 텍스트를 병기(NFR-ACC-003). 대시보드에는 근거 출처를 표시하지 않는다(REQ-CHAL-011 참조).</t>
-        </is>
-      </c>
-      <c r="J48" s="9" t="inlineStr">
-        <is>
-          <t>W08 대시보드 (홈), W11 추이 · 변화 추적</t>
-        </is>
-      </c>
-      <c r="K48" s="9" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="27" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>REQ-DASH-011</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>대시보드</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>재평가</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>시점</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="inlineStr">
-        <is>
-          <t>안내</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>챌린지 사이클(4주)이 끝나면 생활습관 재설문과 혈압 중심의 중간 피드백을 안내하고, 전체 검진값 재입력은 3~6개월 주기로 따로 안내해야 한다.</t>
-        </is>
-      </c>
-      <c r="G49" s="11" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>4주 종료 시 주 버튼은 중간 재평가로 전환한다. 전체 재입력 안내는 마지막 전체 입력일로부터 3개월이 지난 뒤 노출한다.</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="inlineStr">
-        <is>
-          <t>W08 대시보드 (홈)</t>
-        </is>
-      </c>
-      <c r="K49" s="11" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="40.5" customHeight="1">
-      <c r="A50" s="18" t="inlineStr">
-        <is>
-          <t>NFR-DASH-001</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="inlineStr">
-        <is>
-          <t>대시보드</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>동기</t>
-        </is>
-      </c>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>보상</t>
-        </is>
-      </c>
-      <c r="E50" s="19" t="inlineStr">
-        <is>
-          <t>MVP 범위</t>
-        </is>
-      </c>
-      <c r="F50" s="19" t="inlineStr">
-        <is>
-          <t>MVP 단계의 대시보드는 포인트·쿠폰 등 외재적 보상 없이 위험도·혈압 변화와 주간 달성률만으로 동기를 제시한다.</t>
-        </is>
-      </c>
-      <c r="G50" s="19" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H50" s="19" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="I50" s="19" t="inlineStr">
-        <is>
-          <t>리워드 UI 미존재. 유지율 추이를 확인한 뒤 소셜·리워드 요소를 단계적으로 재검토하며, 재검토 시점과 기준을 문서로 남긴다. 개인 인증률·연속 수행일 기반 배지·포인트는 Phase 2 후보로 두며, 재원과 부정 인증 방지 정책을 먼저 정한다. (PRD CH-08)</t>
-        </is>
-      </c>
-      <c r="J50" s="19" t="inlineStr">
-        <is>
-          <t>W08 대시보드 (홈), W09 챌린지 선택, W10 챌린지 수행 · 인증</t>
-        </is>
-      </c>
-      <c r="K50" s="19" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="27" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>REQ-RECO-001</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>추천</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>LLM 생성</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>근거 기반</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>행동 제안</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>사용자는 예측 결과와 승인된 건강정보를 근거로 생성된 예방 행동 제안을 확인할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>제안마다 근거 출처와 생성 시각을 표시. 약물·처방 관련 제안 금지.</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>W06 예측 결과 · XAI 설명</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="27" customHeight="1">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>REQ-RECO-002</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t>추천</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>식단 분석</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>나트륨 점수화</t>
-        </is>
-      </c>
-      <c r="E52" s="11" t="inlineStr">
-        <is>
-          <t>이미지 인식</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>사용자는 식단 사진을 올려 나트륨 중심의 점수와 개선 제안을 확인할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H52" s="11" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>점수 기준은 칼로리가 아닌 나트륨. 음식별 영양소는 식약처 공개 데이터를 기준으로 한다. 분석 실패 시 직접 입력으로 대체 가능.</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>W10 챌린지 수행 · 인증</t>
-        </is>
-      </c>
-      <c r="K52" s="11" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="40.5" customHeight="1">
-      <c r="A53" s="18" t="inlineStr">
-        <is>
-          <t>REQ-NOTI-001</t>
-        </is>
-      </c>
-      <c r="B53" s="19" t="inlineStr">
-        <is>
-          <t>알림</t>
-        </is>
-      </c>
-      <c r="C53" s="19" t="inlineStr">
-        <is>
-          <t>리마인더</t>
-        </is>
-      </c>
-      <c r="D53" s="19" t="inlineStr">
-        <is>
-          <t>시작 알림</t>
-        </is>
-      </c>
-      <c r="E53" s="19" t="inlineStr">
-        <is>
-          <t>발송 시각</t>
-        </is>
-      </c>
-      <c r="F53" s="19" t="inlineStr">
-        <is>
-          <t>사용자는 아침 지정 시각에 그날의 챌린지 시작 알림을 받을 수 있어야 한다. 문구는 참여를 강요하지 않는 톤으로 한다.</t>
-        </is>
-      </c>
-      <c r="G53" s="19" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H53" s="19" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I53" s="19" t="inlineStr">
-        <is>
-          <t>사용자별 수신 설정을 따르며 미설정 시 발송하지 않는다. 발송 시각은 사용자가 바꿀 수 있다. 웹 푸시는 HTTPS와 사용자 동작으로 받은 권한이 있을 때만 발송한다. 알림 설정과 개인정보 안내를 같은 화면에서 확인할 수 있게 한다. (PRD CH-09)</t>
-        </is>
-      </c>
-      <c r="J53" s="19" t="inlineStr">
-        <is>
-          <t>W12 피드백 · 마이페이지</t>
-        </is>
-      </c>
-      <c r="K53" s="19" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>REQ-FEED-001</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>피드백</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>결과·추천</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>의견 수집</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>저장</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>사용자는 예측 결과와 추천에 대한 평가와 의견을 남길 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>평가 대상(예측/추천)과 대상 버전을 함께 저장.</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>W12 피드백 · 마이페이지</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>쉬움·적당·어려움 3단계로 저장. 다음 사이클 난이도 추천에 반영되는 것을 확인.</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>W11 추이 · 변화 추적</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -7518,7 +7676,7 @@
     <row r="55" ht="27" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>REQ-FEED-002</t>
+          <t>REQ-FEED-003</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -7528,22 +7686,22 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>챌린지</t>
+          <t>추천</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>난이도</t>
+          <t>거절 사유</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>사이클 종료 평가</t>
+          <t>선택적 수집</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>사용자는 사이클 종료 시 수행한 챌린지의 난이도를 평가할 수 있어야 한다.</t>
+          <t>추천한 챌린지를 선택하지 않은 경우 사유를 선택적으로 수집할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -7553,191 +7711,191 @@
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>"이미 하고 있음 / 관심 없음 / 실천이 어려움" 중 선택. 응답은 선택 사항.</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>W09 챌린지 선택</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="27" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>NFR-FEED-001</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>개선</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>활용 이력</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>수집한 피드백은 분석 리포트와 개선 후보로 연결되어야 한다.</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>쉬움·적당·어려움 3단계로 저장. 다음 사이클 난이도 추천에 반영되는 것을 확인.</t>
-        </is>
-      </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>W11 추이 · 변화 추적</t>
-        </is>
-      </c>
-      <c r="K55" s="9" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>피드백 통계와 개선 반영 이력을 제출.</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="27" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>REQ-FEED-003</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>NFR-FEED-002</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>피드백</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>추천</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>거절 사유</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>선택적 수집</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>추천한 챌린지를 선택하지 않은 경우 사유를 선택적으로 수집할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H56" s="9" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>"이미 하고 있음 / 관심 없음 / 실천이 어려움" 중 선택. 응답은 선택 사항.</t>
-        </is>
-      </c>
-      <c r="J56" s="9" t="inlineStr">
-        <is>
-          <t>W09 챌린지 선택</t>
-        </is>
-      </c>
-      <c r="K56" s="9" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>설문</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>파생 가중치</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>보정 가능</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>설문 응답에서 파생 피처를 만들 때 쓰는 가중치는 피드백과 실측 데이터로 보정할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>가중치를 코드가 아닌 설정으로 관리하고 변경 이력을 남긴다.</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>NFR-FEED-001</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>피드백</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>개선</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>활용 이력</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>수집한 피드백은 분석 리포트와 개선 후보로 연결되어야 한다.</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
+    <row r="58" ht="27" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-001</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>안전성</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>결과 표현</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>위험 선별</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>면책 안내</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>모든 예측 결과 화면에 진단이 아닌 선별 정보라는 면책 문구를 표시해야 한다.</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>피드백 통계와 개선 반영 이력을 제출.</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="27" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>NFR-FEED-002</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>피드백</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>설문</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>파생 가중치</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>보정 가능</t>
-        </is>
-      </c>
-      <c r="F58" s="9" t="inlineStr">
-        <is>
-          <t>설문 응답에서 파생 피처를 만들 때 쓰는 가중치는 피드백과 실측 데이터로 보정할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H58" s="9" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>가중치를 코드가 아닌 설정으로 관리하고 변경 이력을 남긴다.</t>
-        </is>
-      </c>
-      <c r="J58" s="9" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K58" s="9" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>결과가 표시되는 모든 화면·API 응답에 면책 문구 포함.</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>W06 예측 결과 · XAI 설명, W07 검사 · 상담 안내, W08 대시보드 (홈)</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -7746,7 +7904,7 @@
     <row r="59" ht="40.5" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>NFR-SAFE-001</t>
+          <t>NFR-SAFE-002</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -7756,22 +7914,22 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>결과 표현</t>
+          <t>금지 행동</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>위험 선별</t>
+          <t>약물</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>면책 안내</t>
+          <t>처방 제한</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>모든 예측 결과 화면에 진단이 아닌 선별 정보라는 면책 문구를 표시해야 한다.</t>
+          <t>서비스는 약물 복용·변경·중단을 권고하지 않는다.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -7786,12 +7944,12 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>결과가 표시되는 모든 화면·API 응답에 면책 문구 포함.</t>
+          <t>LLM 응답에 안전 필터 적용. 금지 질의는 의료기관 문의로 안내.</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>W06 예측 결과 · XAI 설명, W07 검사 · 상담 안내, W08 대시보드 (홈)</t>
+          <t>W06 예측 결과 · XAI 설명</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
@@ -7803,7 +7961,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>NFR-SAFE-002</t>
+          <t>NFR-SAFE-003</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -7813,22 +7971,22 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>금지 행동</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>약물</t>
+          <t>불확실성</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>처방 제한</t>
+          <t>과도한 확신 방지</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>서비스는 약물 복용·변경·중단을 권고하지 않는다.</t>
+          <t>예측 결과를 확정 발병 확률로 표현하지 않는다.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -7843,7 +8001,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>LLM 응답에 안전 필터 적용. 금지 질의는 의료기관 문의로 안내.</t>
+          <t>확률 단정 표현 금지. 범주형 위험 신호로 표시.</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
@@ -7858,114 +8016,114 @@
       </c>
     </row>
     <row r="61" ht="27" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>NFR-SAFE-003</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-004</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>안전성</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>불확실성</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>과도한 확신 방지</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>예측 결과를 확정 발병 확률로 표현하지 않는다.</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>응급</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>선별</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>즉시 안내</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>응급 의심 증상을 선택한 사용자에게는 예측을 진행하지 않고 즉시 응급 연락 안내를 표시한다.</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" s="9" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>확률 단정 표현 금지. 범주형 위험 신호로 표시.</t>
-        </is>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>W06 예측 결과 · XAI 설명</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>응급 문진 양성 시 입력·예측 화면 진입을 막고 안내만 노출(REQ-ELIG-003 연계).</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>W03 이용 적합성 · 응급 확인</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="62" ht="27" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>NFR-SAFE-004</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-005</t>
+        </is>
+      </c>
+      <c r="B62" s="23" t="inlineStr">
         <is>
           <t>안전성</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>응급</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>선별</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>즉시 안내</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>응급 의심 증상을 선택한 사용자에게는 예측을 진행하지 않고 즉시 응급 연락 안내를 표시한다.</t>
-        </is>
-      </c>
-      <c r="G62" s="9" t="inlineStr">
+      <c r="C62" s="23" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="inlineStr">
+        <is>
+          <t>잠정값</t>
+        </is>
+      </c>
+      <c r="E62" s="23" t="inlineStr">
+        <is>
+          <t>고지</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>학습 데이터가 확정되기 전의 잠정 모델을 사용하는 동안에는 결과 화면에 그 사실을 고지해야 한다.</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H62" s="9" t="inlineStr">
+      <c r="H62" s="23" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>응급 문진 양성 시 입력·예측 화면 진입을 막고 안내만 노출(REQ-ELIG-003 연계).</t>
-        </is>
-      </c>
-      <c r="J62" s="9" t="inlineStr">
-        <is>
-          <t>W03 이용 적합성 · 응급 확인</t>
-        </is>
-      </c>
-      <c r="K62" s="9" t="inlineStr">
+      <c r="I62" s="23" t="inlineStr">
+        <is>
+          <t>결과 화면에 모델의 확정 여부를 표기한다. 확정 후 문구를 제거하는 절차를 정의한다.</t>
+        </is>
+      </c>
+      <c r="J62" s="23" t="inlineStr">
+        <is>
+          <t>W06 예측 결과 · XAI 설명, W08 대시보드 (홈), W11 추이 · 변화 추적</t>
+        </is>
+      </c>
+      <c r="K62" s="23" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -7974,7 +8132,7 @@
     <row r="63" ht="40.5" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>NFR-SAFE-005</t>
+          <t>NFR-SAFE-006</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -7984,22 +8142,22 @@
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>모델</t>
+          <t>톤</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>잠정값</t>
+          <t>상업적 표현</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>고지</t>
+          <t>금지</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>학습 데이터가 확정되기 전의 잠정 모델을 사용하는 동안에는 결과 화면에 그 사실을 고지해야 한다.</t>
+          <t>예측·챌린지 화면에 이벤트성 배너, 광고, 제휴 콘텐츠를 노출하지 않는다.</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr">
@@ -8009,17 +8167,17 @@
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>결과 화면에 학습 데이터 출처와 확정 여부를 표기. 확정 후 문구 제거 절차를 정의.</t>
+          <t>해당 영역은 자체 생성 콘텐츠로만 채운다. 외부 제휴 링크 미존재.</t>
         </is>
       </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>W06 예측 결과 · XAI 설명, W08 대시보드 (홈), W11 추이 · 변화 추적</t>
+          <t>전 화면</t>
         </is>
       </c>
       <c r="K63" s="9" t="inlineStr">
@@ -8031,7 +8189,7 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>NFR-SAFE-006</t>
+          <t>NFR-SAFE-007</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -8041,22 +8199,22 @@
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>톤</t>
+          <t>추천</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>상업적 표현</t>
+          <t>복약</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>금지</t>
+          <t>중단 유도 금지</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>예측·챌린지 화면에 이벤트성 배너, 광고, 제휴 콘텐츠를 노출하지 않는다.</t>
+          <t>고혈압 약을 복용 중이라고 응답한 사용자에게 복약 중단·감량을 시사하는 문구를 노출하지 않는다.</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr">
@@ -8066,17 +8224,17 @@
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>해당 영역은 자체 생성 콘텐츠로만 채운다. 외부 제휴 링크 미존재.</t>
+          <t>복약 응답자에게는 생활습관 개선 문구만 제시(NFR-SAFE-002 연계).</t>
         </is>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>전 화면</t>
+          <t>W06 예측 결과 · XAI 설명, W09 챌린지 선택</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr">
@@ -8086,57 +8244,57 @@
       </c>
     </row>
     <row r="65" ht="27" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>NFR-SAFE-007</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>안전성</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>추천</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>복약</t>
-        </is>
-      </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>중단 유도 금지</t>
-        </is>
-      </c>
-      <c r="F65" s="9" t="inlineStr">
-        <is>
-          <t>고혈압 약을 복용 중이라고 응답한 사용자에게 복약 중단·감량을 시사하는 문구를 노출하지 않는다.</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>NFR-SEC-001</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>비밀번호</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>해시 저장</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>비밀번호는 검증 가능한 해시로 저장해야 한다.</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H65" s="9" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>복약 응답자에게는 생활습관 개선 문구만 제시(NFR-SAFE-002 연계).</t>
-        </is>
-      </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t>W06 예측 결과 · XAI 설명, W09 챌린지 선택</t>
-        </is>
-      </c>
-      <c r="K65" s="9" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>평문·가역 암호화 저장 금지.</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -8145,7 +8303,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>NFR-SEC-001</t>
+          <t>NFR-SEC-002</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8155,22 +8313,22 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>인증</t>
+          <t>권한</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>비밀번호</t>
+          <t>소유권</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>해시 저장</t>
+          <t>접근 통제</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>비밀번호는 검증 가능한 해시로 저장해야 한다.</t>
+          <t>개인 API는 JWT를 검증하고 자원 소유자 본인만 접근할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -8185,7 +8343,7 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>평문·가역 암호화 저장 금지.</t>
+          <t>타 사용자 자원 접근 시 403. 토큰 없음·만료 401.</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
@@ -8202,7 +8360,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>NFR-SEC-002</t>
+          <t>NFR-SEC-003</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -8212,22 +8370,22 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>권한</t>
+          <t>수집</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>소유권</t>
+          <t>최소화</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>접근 통제</t>
+          <t>목적 제한</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>개인 API는 JWT를 검증하고 자원 소유자 본인만 접근할 수 있어야 한다.</t>
+          <t>서비스 목적에 필요한 최소 건강정보만 수집한다.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -8242,12 +8400,12 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>타 사용자 자원 접근 시 403. 토큰 없음·만료 401.</t>
+          <t>수집 항목별 목적을 동의서에 명시.</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>W02 회원가입 · 로그인 · 동의, W04 건강정보 입력</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -8259,7 +8417,7 @@
     <row r="68" ht="27" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>NFR-SEC-003</t>
+          <t>NFR-SEC-004</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -8269,22 +8427,22 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>수집</t>
+          <t>로그</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>최소화</t>
+          <t>민감정보</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>목적 제한</t>
+          <t>마스킹</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>서비스 목적에 필요한 최소 건강정보만 수집한다.</t>
+          <t>로그와 URL에 건강정보·식별정보를 포함하지 않는다.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -8299,12 +8457,12 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>수집 항목별 목적을 동의서에 명시.</t>
+          <t>민감 필드는 마스킹 후 기록. URL 쿼리에 건강정보 금지.</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>W02 회원가입 · 로그인 · 동의, W04 건강정보 입력</t>
+          <t>해당 없음</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
@@ -8314,57 +8472,57 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>NFR-SEC-004</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>NFR-SEC-005</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>보안</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>로그</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>민감정보</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>마스킹</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>로그와 URL에 건강정보·식별정보를 포함하지 않는다.</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>검진 결과지</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>보관 최소화</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>검진 결과지 업로드 이미지는 값 추출 처리 후 지체 없이 삭제하고 추출된 수치만 저장한다.</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" s="9" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>민감 필드는 마스킹 후 기록. URL 쿼리에 건강정보 금지.</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="inlineStr">
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>원본 이미지 보관 기간을 동의서에 명시. 처리 후 삭제 사실을 로그로 확인.</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>W04 건강정보 입력</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -8373,7 +8531,7 @@
     <row r="70" ht="27" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>NFR-SEC-005</t>
+          <t>NFR-SEC-006</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -8383,22 +8541,22 @@
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>이미지</t>
+          <t>수집</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>검진 결과지</t>
+          <t>설문 응답</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>보관 최소화</t>
+          <t>건강정보 취급</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>검진 결과지 업로드 이미지는 값 추출 처리 후 지체 없이 삭제하고 추출된 수치만 저장한다.</t>
+          <t>생활습관 설문 응답도 건강정보로 분류해 동일한 보호 조치를 적용한다.</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
@@ -8413,12 +8571,12 @@
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>원본 이미지 보관 기간을 동의서에 명시. 처리 후 삭제 사실을 로그로 확인.</t>
+          <t>설문 항목을 동의서 수집 항목에 포함. 암호화·접근통제 대상에 포함(NFR-SEC-002, 003 연계).</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>W04 건강정보 입력</t>
+          <t>W02 회원가입 · 로그인 · 동의, W04 건강정보 입력</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
@@ -8430,7 +8588,7 @@
     <row r="71" ht="27" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>NFR-SEC-006</t>
+          <t>NFR-SEC-007</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -8440,22 +8598,22 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>수집</t>
+          <t>목적 제한</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>설문 응답</t>
+          <t>외부 제공</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>건강정보 취급</t>
+          <t>금지·고지</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>생활습관 설문 응답도 건강정보로 분류해 동일한 보호 조치를 적용한다.</t>
+          <t>수집한 건강정보를 서비스 목적 외로 이용하거나 제3자에게 제공하지 않으며, 그 사실을 입력 화면에 명시한다.</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr">
@@ -8470,12 +8628,12 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>설문 항목을 동의서 수집 항목에 포함. 암호화·접근통제 대상에 포함(NFR-SEC-002, 003 연계).</t>
+          <t>입력 화면에 고지 문구를 노출하고, 외부 전송 경로가 없음을 코드로 증빙.</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">
         <is>
-          <t>W02 회원가입 · 로그인 · 동의, W04 건강정보 입력</t>
+          <t>W04 건강정보 입력</t>
         </is>
       </c>
       <c r="K71" s="9" t="inlineStr">
@@ -8485,57 +8643,57 @@
       </c>
     </row>
     <row r="72" ht="27" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>NFR-SEC-007</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>목적 제한</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>외부 제공</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>금지·고지</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>수집한 건강정보를 서비스 목적 외로 이용하거나 제3자에게 제공하지 않으며, 그 사실을 입력 화면에 명시한다.</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>NFR-ACC-001</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>접근성</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>시각</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>글자·대비</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>고령자 지원</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>본문 텍스트 대비와 최소 글자 크기 기준을 충족해야 한다.</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H72" s="9" t="inlineStr">
+      <c r="H72" s="5" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>입력 화면에 고지 문구를 노출하고, 외부 전송 경로가 없음을 코드로 증빙.</t>
-        </is>
-      </c>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
-          <t>W04 건강정보 입력</t>
-        </is>
-      </c>
-      <c r="K72" s="9" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>본문 대비 4.5:1 이상. 본문 최소 16px.</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>전 화면</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -8544,7 +8702,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>NFR-ACC-001</t>
+          <t>NFR-ACC-002</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -8554,22 +8712,22 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>시각</t>
+          <t>조작</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>글자·대비</t>
+          <t>터치 영역</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>고령자 지원</t>
+          <t>오입력 방지</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>본문 텍스트 대비와 최소 글자 크기 기준을 충족해야 한다.</t>
+          <t>주요 터치 대상은 충분한 크기를 확보해야 한다.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -8579,12 +8737,12 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>본문 대비 4.5:1 이상. 본문 최소 16px.</t>
+          <t>터치 대상 최소 44x44px.</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
@@ -8601,7 +8759,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>NFR-ACC-002</t>
+          <t>NFR-ACC-003</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8611,22 +8769,22 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>조작</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>터치 영역</t>
+          <t>비색상 정보</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>오입력 방지</t>
+          <t>중복 표현</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>주요 터치 대상은 충분한 크기를 확보해야 한다.</t>
+          <t>상태를 색상만으로 구분하지 않는다.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -8636,12 +8794,12 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>터치 대상 최소 44x44px.</t>
+          <t>색상 + 아이콘 또는 텍스트를 함께 제공.</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
@@ -8658,7 +8816,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NFR-ACC-003</t>
+          <t>NFR-ACC-004</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -8668,22 +8826,22 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>키보드·보조기술</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>비색상 정보</t>
+          <t>폼</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>중복 표현</t>
+          <t>레이블·초점</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>상태를 색상만으로 구분하지 않는다.</t>
+          <t>모든 입력 요소에 레이블을 연결하고 키보드로 조작할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -8693,12 +8851,12 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>색상 + 아이콘 또는 텍스트를 함께 제공.</t>
+          <t>탭 순서가 시각적 순서와 일치. 초점 표시 유지.</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
@@ -8715,32 +8873,32 @@
     <row r="76" ht="27" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>NFR-ACC-004</t>
+          <t>NFR-UX-001</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>접근성</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>키보드·보조기술</t>
+          <t>탐색</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>폼</t>
+          <t>핵심 기능</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>레이블·초점</t>
+          <t>3~5회 액션</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>모든 입력 요소에 레이블을 연결하고 키보드로 조작할 수 있어야 한다.</t>
+          <t>핵심 기능은 홈에서 3~5회 이내 액션으로 도달할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -8750,12 +8908,12 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>탭 순서가 시각적 순서와 일치. 초점 표시 유지.</t>
+          <t>핵심 기능별 액션 수 표를 작성해 증빙.</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
@@ -8772,7 +8930,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>NFR-UX-001</t>
+          <t>NFR-UX-002</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -8782,22 +8940,22 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>탐색</t>
+          <t>일관성</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>핵심 기능</t>
+          <t>디자인 시스템</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>3~5회 액션</t>
+          <t>공통 패턴</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>핵심 기능은 홈에서 3~5회 이내 액션으로 도달할 수 있어야 한다.</t>
+          <t>버튼·폼·카드·알림은 공통 컴포넌트를 사용해야 한다.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -8812,7 +8970,7 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>핵심 기능별 액션 수 표를 작성해 증빙.</t>
+          <t>공통 컴포넌트 목록과 사용 화면 매핑을 유지.</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
@@ -8829,32 +8987,32 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>NFR-UX-002</t>
+          <t>NFR-API-001</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>HTTP Method·URI</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
           <t>일관성</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>디자인 시스템</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>공통 패턴</t>
-        </is>
-      </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>버튼·폼·카드·알림은 공통 컴포넌트를 사용해야 한다.</t>
+          <t>API는 자원 중심 URI와 목적에 맞는 HTTP Method를 사용해야 한다.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -8869,12 +9027,12 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>공통 컴포넌트 목록과 사용 화면 매핑을 유지.</t>
+          <t>조회 GET, 생성 POST, 전체수정 PUT, 부분수정 PATCH, 삭제 DELETE.</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>전 화면</t>
+          <t>해당 없음</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
@@ -8886,7 +9044,7 @@
     <row r="79" ht="27" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>NFR-API-001</t>
+          <t>NFR-API-002</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -8896,22 +9054,22 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>성능</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>HTTP Method·URI</t>
+          <t>전체 API</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>일관성</t>
+          <t>P95 3초</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>API는 자원 중심 URI와 목적에 맞는 HTTP Method를 사용해야 한다.</t>
+          <t>전체 API 응답시간 P95는 3초 이내여야 한다.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -8926,7 +9084,7 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>조회 GET, 생성 POST, 전체수정 PUT, 부분수정 PATCH, 삭제 DELETE.</t>
+          <t>부하 테스트 결과로 증빙. 초과 API는 원인과 개선안을 기록.</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
@@ -8943,32 +9101,32 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>NFR-API-002</t>
+          <t>NFR-ASYNC-001</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>비동기</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>성능</t>
+          <t>AI 추론</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>전체 API</t>
+          <t>작업 큐</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>P95 3초</t>
+          <t>비동기 실행</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>전체 API 응답시간 P95는 3초 이내여야 한다.</t>
+          <t>AI 추론은 작업 큐를 통해 비동기로 실행되어야 한다.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -8983,12 +9141,12 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>부하 테스트 결과로 증빙. 초과 API는 원인과 개선안을 기록.</t>
+          <t>동기 방식 대비 처리량·응답시간 차이를 수치로 제시.</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>W05 입력 검토 · 분석 대기</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
@@ -9000,7 +9158,7 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>NFR-ASYNC-001</t>
+          <t>NFR-ASYNC-002</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
@@ -9010,22 +9168,22 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>AI 추론</t>
+          <t>서버 I/O</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>작업 큐</t>
+          <t>DB·외부 API</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>비동기 실행</t>
+          <t>async 처리</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>AI 추론은 작업 큐를 통해 비동기로 실행되어야 한다.</t>
+          <t>DB와 외부 API 호출은 async I/O로 처리해야 한다.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -9040,12 +9198,12 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>동기 방식 대비 처리량·응답시간 차이를 수치로 제시.</t>
+          <t>블로킹 호출이 이벤트 루프를 점유하지 않음을 확인.</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>W05 입력 검토 · 분석 대기</t>
+          <t>해당 없음</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
@@ -9055,228 +9213,228 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>NFR-ASYNC-002</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>비동기</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>서버 I/O</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>DB·외부 API</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>async 처리</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>DB와 외부 API 호출은 async I/O로 처리해야 한다.</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>NFR-ML-001</t>
+        </is>
+      </c>
+      <c r="B82" s="21" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="C82" s="21" t="inlineStr">
+        <is>
+          <t>데이터 분리</t>
+        </is>
+      </c>
+      <c r="D82" s="21" t="inlineStr">
+        <is>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="E82" s="21" t="inlineStr">
+        <is>
+          <t>누수 방지</t>
+        </is>
+      </c>
+      <c r="F82" s="21" t="inlineStr">
+        <is>
+          <t>학습·검증·테스트를 분리하고 전처리는 학습 데이터 기준으로 적합시켜야 한다.</t>
+        </is>
+      </c>
+      <c r="G82" s="21" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H82" s="21" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>블로킹 호출이 이벤트 루프를 점유하지 않음을 확인.</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
+      <c r="I82" s="21" t="inlineStr">
+        <is>
+          <t>스케일러·인코더를 학습 셋에만 fit. 분리 코드로 증빙. 결측 코드는 변수별 의미에 따라 구분 처리한다(예: 8=비해당·해당 범주 유지, 9=모름/무응답만 결측 처리) — 임의로 통합 처리하지 않는다.</t>
+        </is>
+      </c>
+      <c r="J82" s="21" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K82" s="5" t="inlineStr">
+      <c r="K82" s="21" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="83" ht="27" customHeight="1">
-      <c r="A83" s="20" t="inlineStr">
-        <is>
-          <t>NFR-ML-001</t>
-        </is>
-      </c>
-      <c r="B83" s="21" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>NFR-ML-002</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>모델</t>
         </is>
       </c>
-      <c r="C83" s="21" t="inlineStr">
-        <is>
-          <t>데이터 분리</t>
-        </is>
-      </c>
-      <c r="D83" s="21" t="inlineStr">
-        <is>
-          <t>전처리</t>
-        </is>
-      </c>
-      <c r="E83" s="21" t="inlineStr">
-        <is>
-          <t>누수 방지</t>
-        </is>
-      </c>
-      <c r="F83" s="21" t="inlineStr">
-        <is>
-          <t>학습·검증·테스트를 분리하고 전처리는 학습 데이터 기준으로 적합시켜야 한다.</t>
-        </is>
-      </c>
-      <c r="G83" s="21" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>특징</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>라벨 누수</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>타깃 정보가 새는 특징을 학습에 사용하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H83" s="21" t="inlineStr">
+      <c r="H83" s="5" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I83" s="21" t="inlineStr">
-        <is>
-          <t>스케일러·인코더를 학습 셋에만 fit. 분리 코드로 증빙. 결측 코드는 변수별 의미에 따라 구분 처리한다(예: 8=비해당·해당 범주 유지, 9=모름/무응답만 결측 처리) — 임의로 통합 처리하지 않는다.</t>
-        </is>
-      </c>
-      <c r="J83" s="21" t="inlineStr">
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>특징별 누수 검토 결과를 기록.</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K83" s="21" t="inlineStr">
+      <c r="K83" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>NFR-ML-002</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>NFR-ML-003</t>
+        </is>
+      </c>
+      <c r="B84" s="21" t="inlineStr">
         <is>
           <t>모델</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>라벨 누수</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>검토</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>타깃 정보가 새는 특징을 학습에 사용하지 않는다.</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
+      <c r="C84" s="21" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="D84" s="21" t="inlineStr">
+        <is>
+          <t>분류 지표</t>
+        </is>
+      </c>
+      <c r="E84" s="21" t="inlineStr">
+        <is>
+          <t>비교</t>
+        </is>
+      </c>
+      <c r="F84" s="21" t="inlineStr">
+        <is>
+          <t>2개 이상 모델을 동일 조건에서 비교하고 지표를 기록해야 한다.</t>
+        </is>
+      </c>
+      <c r="G84" s="21" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="H84" s="21" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>특징별 누수 검토 결과를 기록.</t>
-        </is>
-      </c>
-      <c r="J84" s="5" t="inlineStr">
+      <c r="I84" s="21" t="inlineStr">
+        <is>
+          <t>평가지표는 AUC-ROC를 기본으로 하고 F1-score·혼동행렬을 함께 기록한다. 로지스틱회귀(베이스라인)와 트리 계열 모델(XGBoost 또는 LightGBM) 최소 2종을 동일 조건에서 비교한다. 실험표·혼동행렬·개선 전후 결과를 제출.</t>
+        </is>
+      </c>
+      <c r="J84" s="21" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K84" s="5" t="inlineStr">
+      <c r="K84" s="21" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>NFR-ML-003</t>
-        </is>
-      </c>
-      <c r="B85" s="21" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>NFR-ML-004</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>모델</t>
         </is>
       </c>
-      <c r="C85" s="21" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="D85" s="21" t="inlineStr">
-        <is>
-          <t>분류 지표</t>
-        </is>
-      </c>
-      <c r="E85" s="21" t="inlineStr">
-        <is>
-          <t>비교</t>
-        </is>
-      </c>
-      <c r="F85" s="21" t="inlineStr">
-        <is>
-          <t>2개 이상 모델을 동일 조건에서 비교하고 지표를 기록해야 한다.</t>
-        </is>
-      </c>
-      <c r="G85" s="21" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>재현성</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>버전</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>모델·전처리·임계값 버전을 예측 결과와 함께 저장해야 한다.</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H85" s="21" t="inlineStr">
+      <c r="H85" s="5" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I85" s="21" t="inlineStr">
-        <is>
-          <t>평가지표는 AUC-ROC를 기본으로 하고 F1-score·혼동행렬을 함께 기록한다. 로지스틱회귀(베이스라인)와 트리 계열 모델(XGBoost 또는 LightGBM) 최소 2종을 동일 조건에서 비교한다. 실험표·혼동행렬·개선 전후 결과를 제출.</t>
-        </is>
-      </c>
-      <c r="J85" s="21" t="inlineStr">
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>예측 레코드에서 사용된 모델 버전을 역추적할 수 있다.</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K85" s="21" t="inlineStr">
+      <c r="K85" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -9285,7 +9443,7 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>NFR-ML-004</t>
+          <t>NFR-ML-005</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
@@ -9295,22 +9453,22 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>재현성</t>
+          <t>일관성</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>버전</t>
+          <t>동일 입력</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>반복 검증</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>모델·전처리·임계값 버전을 예측 결과와 함께 저장해야 한다.</t>
+          <t>동일 입력에 대해 반복 예측 시 결과가 일치해야 한다.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -9325,7 +9483,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>예측 레코드에서 사용된 모델 버전을 역추적할 수 있다.</t>
+          <t>100건 x 10회 반복 테스트에서 점수 편차 0.</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
@@ -9340,114 +9498,114 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>NFR-ML-005</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="A87" s="20" t="inlineStr">
+        <is>
+          <t>NFR-ML-006</t>
+        </is>
+      </c>
+      <c r="B87" s="21" t="inlineStr">
         <is>
           <t>모델</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>일관성</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>동일 입력</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>반복 검증</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>동일 입력에 대해 반복 예측 시 결과가 일치해야 한다.</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="C87" s="21" t="inlineStr">
+        <is>
+          <t>재학습</t>
+        </is>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
+        <is>
+          <t>누적 데이터</t>
+        </is>
+      </c>
+      <c r="E87" s="21" t="inlineStr">
+        <is>
+          <t>주기</t>
+        </is>
+      </c>
+      <c r="F87" s="21" t="inlineStr">
+        <is>
+          <t>챌린지 후보로 채택되는 생활습관 피처는 학습 데이터에서 라벨과의 상관관계 또는 유의미한 영향력이 사전에 검증된 것이어야 한다.</t>
+        </is>
+      </c>
+      <c r="G87" s="21" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H87" s="21" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I87" s="21" t="inlineStr">
+        <is>
+          <t>피처별 SHAP 중요도 평균(절댓값) 상위 5위 이내이거나, 라벨과의 상관계수 절댓값이 0.1 이상인 피처만 챌린지 후보로 채택한다. 기준 미달 피처는 챌린지 후보에서 제외하거나 참고용으로만 표시한다. 분석 결과는 REQ-CHAL의 고정·선택 미션 분류 근거로 사용한다.</t>
+        </is>
+      </c>
+      <c r="J87" s="21" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K87" s="21" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="27" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>NFR-ARCH-001</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>아키텍처</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>계층 분리</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>FastAPI</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>의존성 방향</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>API·서비스·저장소·도메인·ML 추론 계층을 분리하고 의존성 방향을 단방향으로 유지한다.</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
-        <is>
-          <t>100건 x 10회 반복 테스트에서 점수 편차 0.</t>
-        </is>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>아키텍처 다이어그램과 패키지 구조로 증빙.</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K87" s="5" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="27" customHeight="1">
-      <c r="A88" s="20" t="inlineStr">
-        <is>
-          <t>NFR-ML-006</t>
-        </is>
-      </c>
-      <c r="B88" s="21" t="inlineStr">
-        <is>
-          <t>모델</t>
-        </is>
-      </c>
-      <c r="C88" s="21" t="inlineStr">
-        <is>
-          <t>재학습</t>
-        </is>
-      </c>
-      <c r="D88" s="21" t="inlineStr">
-        <is>
-          <t>누적 데이터</t>
-        </is>
-      </c>
-      <c r="E88" s="21" t="inlineStr">
-        <is>
-          <t>주기</t>
-        </is>
-      </c>
-      <c r="F88" s="21" t="inlineStr">
-        <is>
-          <t>챌린지 후보로 채택되는 생활습관 피처는 학습 데이터에서 라벨과의 상관관계 또는 유의미한 영향력이 사전에 검증된 것이어야 한다.</t>
-        </is>
-      </c>
-      <c r="G88" s="21" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H88" s="21" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I88" s="21" t="inlineStr">
-        <is>
-          <t>피처별 SHAP 중요도 평균(절댓값) 상위 5위 이내이거나, 라벨과의 상관계수 절댓값이 0.1 이상인 피처만 챌린지 후보로 채택한다. 기준 미달 피처는 챌린지 후보에서 제외하거나 참고용으로만 표시한다. 분석 결과는 REQ-CHAL의 고정·선택 미션 분류 근거로 사용한다.</t>
-        </is>
-      </c>
-      <c r="J88" s="21" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K88" s="21" t="inlineStr">
+      <c r="K88" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -9456,7 +9614,7 @@
     <row r="89" ht="27" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>NFR-ARCH-001</t>
+          <t>NFR-ARCH-002</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -9466,22 +9624,22 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>계층 분리</t>
+          <t>확장성</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>질환·모델</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>의존성 방향</t>
+          <t>인터페이스</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>API·서비스·저장소·도메인·ML 추론 계층을 분리하고 의존성 방향을 단방향으로 유지한다.</t>
+          <t>질환과 모델을 추가할 때 기존 로직 수정 없이 확장할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -9496,7 +9654,7 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>아키텍처 다이어그램과 패키지 구조로 증빙.</t>
+          <t>확장 시나리오 1건을 문서로 제시.</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
@@ -9511,57 +9669,57 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>NFR-ARCH-002</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>NFR-ARCH-003</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
         <is>
           <t>아키텍처</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>확장성</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>질환·모델</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>인터페이스</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>질환과 모델을 추가할 때 기존 로직 수정 없이 확장할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>A · B 분리</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>독립 배포</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>모델 A와 모델 B를 각각 독립적으로 교체·배포할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H90" s="5" t="inlineStr">
+      <c r="H90" s="9" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>확장 시나리오 1건을 문서로 제시.</t>
-        </is>
-      </c>
-      <c r="J90" s="5" t="inlineStr">
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>모델별 버전과 추론 경로를 분리한다. 한쪽 교체가 다른 쪽 결과에 영향을 주지 않음을 확인한다.</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K90" s="5" t="inlineStr">
+      <c r="K90" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -9570,7 +9728,7 @@
     <row r="91" ht="27" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>NFR-ARCH-003</t>
+          <t>NFR-ARCH-004</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -9580,22 +9738,22 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>모델</t>
+          <t>비교</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>A · B 분리</t>
+          <t>모델 버전</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>독립 배포</t>
+          <t>고정</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>모델 A와 모델 B를 각각 독립적으로 교체·배포할 수 있어야 한다.</t>
+          <t>전·후 비교는 동일한 모델 버전으로 계산해야 하며, 모든 예측 결과에 사용한 모델 버전을 함께 저장한다.</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
@@ -9610,12 +9768,12 @@
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>모델별 버전과 추론 경로를 분리한다. 한쪽 교체가 다른 쪽 결과에 영향을 주지 않음을 확인한다.</t>
+          <t>비교 대상 두 결과의 모델 버전이 다르면 비교를 표시하지 않고 안내 문구로 대체한다.</t>
         </is>
       </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>W11 추이 · 변화 추적</t>
         </is>
       </c>
       <c r="K91" s="9" t="inlineStr">
@@ -9627,7 +9785,7 @@
     <row r="92" ht="27" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>NFR-ARCH-004</t>
+          <t>NFR-ARCH-005</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -9637,22 +9795,22 @@
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>비교</t>
+          <t>설정</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>모델 버전</t>
+          <t>챌린지·설문</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>고정</t>
+          <t>데이터 주도</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>전·후 비교는 동일한 모델 버전으로 계산해야 하며, 모든 예측 결과에 사용한 모델 버전을 함께 저장한다.</t>
+          <t>챌린지 카테고리·미션과 설문 문항은 코드 수정 없이 데이터로 추가·변경할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G92" s="9" t="inlineStr">
@@ -9662,17 +9820,17 @@
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>비교 대상 두 결과의 모델 버전이 다르면 비교를 표시하지 않고 안내 문구로 대체한다.</t>
+          <t>미션 1건 추가가 배포 없이 반영되는 것을 시연.</t>
         </is>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>W11 추이 · 변화 추적</t>
+          <t>해당 없음</t>
         </is>
       </c>
       <c r="K92" s="9" t="inlineStr">
@@ -9682,57 +9840,57 @@
       </c>
     </row>
     <row r="93" ht="27" customHeight="1">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>NFR-ARCH-005</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>아키텍처</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>챌린지·설문</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>데이터 주도</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="inlineStr">
-        <is>
-          <t>챌린지 카테고리·미션과 설문 문항은 코드 수정 없이 데이터로 추가·변경할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G93" s="9" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>NFR-OPS-001</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>상태 점검</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>서비스</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>헬스 체크</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>배포된 서비스는 상태 점검 엔드포인트를 제공해야 한다.</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H93" s="9" t="inlineStr">
+      <c r="H93" s="5" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="I93" s="9" t="inlineStr">
-        <is>
-          <t>미션 1건 추가가 배포 없이 반영되는 것을 시연.</t>
-        </is>
-      </c>
-      <c r="J93" s="9" t="inlineStr">
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>GET /health 200. DB·큐 연결 상태 포함.</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K93" s="9" t="inlineStr">
+      <c r="K93" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -9741,7 +9899,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>NFR-OPS-001</t>
+          <t>NFR-OPS-002</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -9751,22 +9909,22 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>상태 점검</t>
+          <t>오류 추적</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>헬스 체크</t>
+          <t>추적 ID</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>배포된 서비스는 상태 점검 엔드포인트를 제공해야 한다.</t>
+          <t>모든 요청에 추적 ID를 부여하고 오류 로그에 포함해야 한다.</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -9781,7 +9939,7 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>GET /health 200. DB·큐 연결 상태 포함.</t>
+          <t>오류 응답과 로그에서 동일 추적 ID로 연결 가능.</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
@@ -9798,7 +9956,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>NFR-OPS-002</t>
+          <t>NFR-OPS-003</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
@@ -9808,22 +9966,22 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>오류 추적</t>
+          <t>배포</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>재현성</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>추적 ID</t>
+          <t>Docker·환경변수</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>모든 요청에 추적 ID를 부여하고 오류 로그에 포함해야 한다.</t>
+          <t>배포는 Docker로 재현 가능해야 하며 비밀값은 환경변수로 주입한다.</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -9833,305 +9991,305 @@
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>코드에 API 키·모델명 하드코딩 금지. .env.example 제공.</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="27" customHeight="1">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>NFR-OPS-004</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>변경 이력</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>모델 버전과 계수 변경 이력을 기록하고 조회할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>오류 응답과 로그에서 동일 추적 ID로 연결 가능.</t>
-        </is>
-      </c>
-      <c r="J95" s="5" t="inlineStr">
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>변경 일시·변경자·사유를 기록. 과거 예측 결과에서 사용 버전을 역추적 가능.</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K95" s="5" t="inlineStr">
+      <c r="K96" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="27" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>NFR-OPS-003</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
+    <row r="97" ht="27" customHeight="1">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>NFR-OPS-005</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>배포</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>재현성</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>Docker·환경변수</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>배포는 Docker로 재현 가능해야 하며 비밀값은 환경변수로 주입한다.</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>배치</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>재평가</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>리마인더 발송</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>사이클 종료 시점의 중간 재평가 안내와 3~6개월 주기의 전체 재검진 안내를 각각 자동으로 발송해야 한다.</t>
+        </is>
+      </c>
+      <c r="G97" s="11" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H96" s="5" t="inlineStr">
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>두 주기의 스케줄을 분리해 관리한다. 작업 실패 시 재시도와 알림(REQ-NOTI-001 연계).</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K97" s="11" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="27" customHeight="1">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>NFR-OPS-006</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>모니터링</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>인식 실패</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>지표 수집</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>검진 결과지 인식 실패율을 지표로 수집해야 한다.</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>실패율이 임계치를 넘으면 직접 입력 안내를 우선 노출하도록 전환.</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>W04 건강정보 입력</t>
+        </is>
+      </c>
+      <c r="K98" s="9" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>NFR-ML-009</t>
+        </is>
+      </c>
+      <c r="B99" s="16" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="C99" s="16" t="inlineStr">
+        <is>
+          <t>재학습</t>
+        </is>
+      </c>
+      <c r="D99" s="16" t="inlineStr">
+        <is>
+          <t>누적 데이터</t>
+        </is>
+      </c>
+      <c r="E99" s="16" t="inlineStr">
+        <is>
+          <t>주기</t>
+        </is>
+      </c>
+      <c r="F99" s="16" t="inlineStr">
+        <is>
+          <t>챌린지 수행으로 쌓인 측정·생활습관 데이터를 모델 재학습에 반영할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G99" s="16" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H99" s="16" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>재학습 주기와 데이터 범위를 문서로 정의한다. 재학습 후 성능 지표를 비교해 기록한다.</t>
+        </is>
+      </c>
+      <c r="J99" s="16" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K99" s="16" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>NFR-ML-007</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>데이터셋</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>모델 이원화</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="inlineStr">
+        <is>
+          <t>독립 학습</t>
+        </is>
+      </c>
+      <c r="F100" s="14" t="inlineStr">
+        <is>
+          <t>모델 A(장기 위험)와 모델 B(현재 위험)는 서로 다른 데이터셋으로 각각 독립적으로 학습하며, 두 데이터를 하나로 합쳐 학습하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H100" s="14" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>코드에 API 키·모델명 하드코딩 금지. .env.example 제공.</t>
-        </is>
-      </c>
-      <c r="J96" s="5" t="inlineStr">
+      <c r="I100" s="14" t="inlineStr">
+        <is>
+          <t>모델 A는 Framingham Heart Study(미국, 코호트, 10년 후 CHD 예측), 모델 B는 국민건강영양조사 2022-2024(한국, 횡단면, 현재 경계군 여부 예측) 데이터셋을 사용한다. 두 모델의 학습 코드·아티팩트(모델 파일·스케일러)는 분리해 관리한다.</t>
+        </is>
+      </c>
+      <c r="J100" s="14" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K96" s="5" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="27" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>NFR-OPS-004</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>모델</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>변경 이력</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>기록</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>모델 버전과 계수 변경 이력을 기록하고 조회할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H97" s="9" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>변경 일시·변경자·사유를 기록. 과거 예측 결과에서 사용 버전을 역추적 가능.</t>
-        </is>
-      </c>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K97" s="9" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="27" customHeight="1">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>NFR-OPS-005</t>
-        </is>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="C98" s="11" t="inlineStr">
-        <is>
-          <t>배치</t>
-        </is>
-      </c>
-      <c r="D98" s="11" t="inlineStr">
-        <is>
-          <t>재평가</t>
-        </is>
-      </c>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>리마인더 발송</t>
-        </is>
-      </c>
-      <c r="F98" s="11" t="inlineStr">
-        <is>
-          <t>사이클 종료 시점의 중간 재평가 안내와 3~6개월 주기의 전체 재검진 안내를 각각 자동으로 발송해야 한다.</t>
-        </is>
-      </c>
-      <c r="G98" s="11" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H98" s="11" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I98" s="11" t="inlineStr">
-        <is>
-          <t>두 주기의 스케줄을 분리해 관리한다. 작업 실패 시 재시도와 알림(REQ-NOTI-001 연계).</t>
-        </is>
-      </c>
-      <c r="J98" s="11" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K98" s="11" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>NFR-OPS-006</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>모니터링</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>인식 실패</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>지표 수집</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>검진 결과지 인식 실패율을 지표로 수집해야 한다.</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H99" s="9" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>실패율이 임계치를 넘으면 직접 입력 안내를 우선 노출하도록 전환.</t>
-        </is>
-      </c>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>W04 건강정보 입력</t>
-        </is>
-      </c>
-      <c r="K99" s="9" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="15" t="inlineStr">
-        <is>
-          <t>NFR-ML-009</t>
-        </is>
-      </c>
-      <c r="B100" s="16" t="inlineStr">
-        <is>
-          <t>모델</t>
-        </is>
-      </c>
-      <c r="C100" s="16" t="inlineStr">
-        <is>
-          <t>재학습</t>
-        </is>
-      </c>
-      <c r="D100" s="16" t="inlineStr">
-        <is>
-          <t>누적 데이터</t>
-        </is>
-      </c>
-      <c r="E100" s="16" t="inlineStr">
-        <is>
-          <t>주기</t>
-        </is>
-      </c>
-      <c r="F100" s="16" t="inlineStr">
-        <is>
-          <t>챌린지 수행으로 쌓인 측정·생활습관 데이터를 모델 재학습에 반영할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G100" s="16" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H100" s="16" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I100" s="16" t="inlineStr">
-        <is>
-          <t>재학습 주기와 데이터 범위를 문서로 정의한다. 재학습 후 성능 지표를 비교해 기록한다.</t>
-        </is>
-      </c>
-      <c r="J100" s="16" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K100" s="16" t="inlineStr">
+      <c r="K100" s="14" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -10140,7 +10298,7 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>NFR-ML-007</t>
+          <t>NFR-ML-008</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
@@ -10150,22 +10308,22 @@
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>데이터셋</t>
+          <t>모집단</t>
         </is>
       </c>
       <c r="D101" s="14" t="inlineStr">
         <is>
-          <t>모델 이원화</t>
+          <t>학습 대상</t>
         </is>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>독립 학습</t>
+          <t>고혈압군 제외</t>
         </is>
       </c>
       <c r="F101" s="14" t="inlineStr">
         <is>
-          <t>모델 A(장기 위험)와 모델 B(현재 위험)는 서로 다른 데이터셋으로 각각 독립적으로 학습하며, 두 데이터를 하나로 합쳐 학습하지 않는다.</t>
+          <t>모델 B의 학습 데이터 모집단은 정상 또는 경계군에 해당하는 응답자로 한정하며, 이미 고혈압(4단계)에 해당하는 응답자는 학습 대상에서 제외한다.</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
@@ -10180,7 +10338,7 @@
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
-          <t>모델 A는 Framingham Heart Study(미국, 코호트, 10년 후 CHD 예측), 모델 B는 국민건강영양조사 2022-2024(한국, 횡단면, 현재 경계군 여부 예측) 데이터셋을 사용한다. 두 모델의 학습 코드·아티팩트(모델 파일·스케일러)는 분리해 관리한다.</t>
+          <t>HE_HP=1(정상), 2·3(경계군)에 해당하는 응답자만 학습에 포함하고, HE_HP=4(고혈압)는 제외한다. 이는 학습 데이터 구성 단계의 필터링이며, 서비스 시점의 사용자 자격 판단(REQ-ELIG-002, 자기보고 기반)과는 별개 기준이다.</t>
         </is>
       </c>
       <c r="J101" s="14" t="inlineStr">
@@ -10197,37 +10355,37 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>NFR-ML-008</t>
+          <t>REQ-PRED-008</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>모델</t>
+          <t>예측·분석</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>모집단</t>
+          <t>결과 입력</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>학습 대상</t>
+          <t>나트륨 설문</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>고혈압군 제외</t>
+          <t>점수화</t>
         </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>모델 B의 학습 데이터 모집단은 정상 또는 경계군에 해당하는 응답자로 한정하며, 이미 고혈압(4단계)에 해당하는 응답자는 학습 대상에서 제외한다.</t>
+          <t>사용자는 나트륨 섭취 수준을 5문항 설문으로 응답하고, 그 응답이 점수화·등급화되어 모델 B의 나트륨 섭취 피처로 반영되어야 한다.</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
-          <t>비기능</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="H102" s="14" t="inlineStr">
@@ -10237,12 +10395,12 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>HE_HP=1(정상), 2·3(경계군)에 해당하는 응답자만 학습에 포함하고, HE_HP=4(고혈압)는 제외한다. 이는 학습 데이터 구성 단계의 필터링이며, 서비스 시점의 사용자 자격 판단(REQ-ELIG-002, 자기보고 기반)과는 별개 기준이다.</t>
+          <t>5개 문항(국물·김치·면류·절임·양념) 각 0~2점, 합산 0~10점. 0~3점=하(≤2,088mg), 4~6점=중(2,088~3,363mg), 7~10점=상(&gt;3,363mg)으로 매핑해 모델 B 입력값으로 사용한다. 등급 컷은 KNHANES 2022-2024 병합 데이터의 나트륨 섭취량 실측 삼분위수 기준이다.</t>
         </is>
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>W04 건강정보 입력</t>
         </is>
       </c>
       <c r="K102" s="14" t="inlineStr">
@@ -10252,114 +10410,114 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="13" t="inlineStr">
-        <is>
-          <t>REQ-PRED-008</t>
-        </is>
-      </c>
-      <c r="B103" s="14" t="inlineStr">
+      <c r="A103" s="26" t="inlineStr">
+        <is>
+          <t>REQ-PRED-009</t>
+        </is>
+      </c>
+      <c r="B103" s="17" t="inlineStr">
         <is>
           <t>예측·분석</t>
         </is>
       </c>
-      <c r="C103" s="14" t="inlineStr">
-        <is>
-          <t>결과 입력</t>
-        </is>
-      </c>
-      <c r="D103" s="14" t="inlineStr">
-        <is>
-          <t>나트륨 설문</t>
-        </is>
-      </c>
-      <c r="E103" s="14" t="inlineStr">
-        <is>
-          <t>점수화</t>
-        </is>
-      </c>
-      <c r="F103" s="14" t="inlineStr">
-        <is>
-          <t>사용자는 나트륨 섭취 수준을 5문항 설문으로 응답하고, 그 응답이 점수화·등급화되어 모델 B의 나트륨 섭취 피처로 반영되어야 한다.</t>
-        </is>
-      </c>
-      <c r="G103" s="14" t="inlineStr">
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>위험 예측</t>
+        </is>
+      </c>
+      <c r="D103" s="17" t="inlineStr">
+        <is>
+          <t>대상군 정의</t>
+        </is>
+      </c>
+      <c r="E103" s="17" t="inlineStr">
+        <is>
+          <t>경계군 분류</t>
+        </is>
+      </c>
+      <c r="F103" s="17" t="inlineStr">
+        <is>
+          <t>모델 B의 라벨은 정상(0) vs 경계군(1, 주의혈압·고혈압전단계)의 이진 분류로 정의한다. 학습 데이터 모집단 구성은 NFR-ML-007을 따른다.</t>
+        </is>
+      </c>
+      <c r="G103" s="17" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H103" s="14" t="inlineStr">
+      <c r="H103" s="17" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I103" s="14" t="inlineStr">
-        <is>
-          <t>5개 문항(국물·김치·면류·절임·양념) 각 0~2점, 합산 0~10점. 0~3점=하(≤2,088mg), 4~6점=중(2,088~3,363mg), 7~10점=상(&gt;3,363mg)으로 매핑해 모델 B 입력값으로 사용한다. 등급 컷은 KNHANES 2022-2024 병합 데이터의 나트륨 섭취량 실측 삼분위수 기준이다.</t>
-        </is>
-      </c>
-      <c r="J103" s="14" t="inlineStr">
-        <is>
-          <t>W04 건강정보 입력</t>
-        </is>
-      </c>
-      <c r="K103" s="14" t="inlineStr">
+      <c r="I103" s="17" t="inlineStr">
+        <is>
+          <t>라벨은 정상(0)/경계군(1) 이진값으로 정의한다. 서비스에서 예측 제공 대상자 판단은 REQ-ELIG-002(자기보고 기반 기진단 여부)를 그대로 따르며, 사용자가 입력한 혈압 수치가 고혈압 기준에 해당하더라도 자기보고상 미진단이면 예측을 제공하고 결과가 위험 단계이면 REQ-PRED-005(검사·상담 안내)로 연결한다. (참고: 학습 데이터에서 HE_HP=4(고혈압) 응답자를 제외하는 것은 훈련 모집단 구성의 문제이며, REQ-ELIG-002의 서비스 시점 자기보고 기준과는 별개다 — NFR-ML-007 참고)</t>
+        </is>
+      </c>
+      <c r="J103" s="17" t="inlineStr">
+        <is>
+          <t>W06 예측 결과 · XAI 설명</t>
+        </is>
+      </c>
+      <c r="K103" s="17" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="26" t="inlineStr">
-        <is>
-          <t>REQ-PRED-009</t>
-        </is>
-      </c>
-      <c r="B104" s="17" t="inlineStr">
-        <is>
-          <t>예측·분석</t>
-        </is>
-      </c>
-      <c r="C104" s="17" t="inlineStr">
-        <is>
-          <t>위험 예측</t>
-        </is>
-      </c>
-      <c r="D104" s="17" t="inlineStr">
-        <is>
-          <t>대상군 정의</t>
-        </is>
-      </c>
-      <c r="E104" s="17" t="inlineStr">
-        <is>
-          <t>경계군 분류</t>
-        </is>
-      </c>
-      <c r="F104" s="17" t="inlineStr">
-        <is>
-          <t>모델 B의 라벨은 정상(0) vs 경계군(1, 주의혈압·고혈압전단계)의 이진 분류로 정의한다. 학습 데이터 모집단 구성은 NFR-ML-007을 따른다.</t>
-        </is>
-      </c>
-      <c r="G104" s="17" t="inlineStr">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>REQ-NOTI-002</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>리마인더</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="inlineStr">
+        <is>
+          <t>건강정보 입력</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>발송</t>
+        </is>
+      </c>
+      <c r="F104" s="14" t="inlineStr">
+        <is>
+          <t>사용자는 건강정보 재입력(재검진) 시점에 알림을 받을 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H104" s="17" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="I104" s="17" t="inlineStr">
-        <is>
-          <t>라벨은 정상(0)/경계군(1) 이진값으로 정의한다. 서비스에서 예측 제공 대상자 판단은 REQ-ELIG-002(자기보고 기반 기진단 여부)를 그대로 따르며, 사용자가 입력한 혈압 수치가 고혈압 기준에 해당하더라도 자기보고상 미진단이면 예측을 제공하고 결과가 위험 단계이면 REQ-PRED-005(검사·상담 안내)로 연결한다. (참고: 학습 데이터에서 HE_HP=4(고혈압) 응답자를 제외하는 것은 훈련 모집단 구성의 문제이며, REQ-ELIG-002의 서비스 시점 자기보고 기준과는 별개다 — NFR-ML-007 참고)</t>
-        </is>
-      </c>
-      <c r="J104" s="17" t="inlineStr">
-        <is>
-          <t>W06 예측 결과 · XAI 설명</t>
-        </is>
-      </c>
-      <c r="K104" s="17" t="inlineStr">
+      <c r="H104" s="14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>사용자별 알림 수신 설정을 따르며 미설정 시 발송하지 않는다.</t>
+        </is>
+      </c>
+      <c r="J104" s="14" t="inlineStr">
+        <is>
+          <t>W12 피드백 · 마이페이지</t>
+        </is>
+      </c>
+      <c r="K104" s="14" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -10368,7 +10526,7 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>REQ-NOTI-002</t>
+          <t>REQ-NOTI-003</t>
         </is>
       </c>
       <c r="B105" s="14" t="inlineStr">
@@ -10383,7 +10541,7 @@
       </c>
       <c r="D105" s="14" t="inlineStr">
         <is>
-          <t>건강정보 입력</t>
+          <t>예방행동가이드 확인</t>
         </is>
       </c>
       <c r="E105" s="14" t="inlineStr">
@@ -10393,7 +10551,7 @@
       </c>
       <c r="F105" s="14" t="inlineStr">
         <is>
-          <t>사용자는 건강정보 재입력(재검진) 시점에 알림을 받을 수 있어야 한다.</t>
+          <t>사용자는 새로 생성된 예방 행동 제안(LLM 추천)을 확인하라는 알림을 받을 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G105" s="14" t="inlineStr">
@@ -10417,63 +10575,6 @@
         </is>
       </c>
       <c r="K105" s="14" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="13" t="inlineStr">
-        <is>
-          <t>REQ-NOTI-003</t>
-        </is>
-      </c>
-      <c r="B106" s="14" t="inlineStr">
-        <is>
-          <t>알림</t>
-        </is>
-      </c>
-      <c r="C106" s="14" t="inlineStr">
-        <is>
-          <t>리마인더</t>
-        </is>
-      </c>
-      <c r="D106" s="14" t="inlineStr">
-        <is>
-          <t>예방행동가이드 확인</t>
-        </is>
-      </c>
-      <c r="E106" s="14" t="inlineStr">
-        <is>
-          <t>발송</t>
-        </is>
-      </c>
-      <c r="F106" s="14" t="inlineStr">
-        <is>
-          <t>사용자는 새로 생성된 예방 행동 제안(LLM 추천)을 확인하라는 알림을 받을 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G106" s="14" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H106" s="14" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-      <c r="I106" s="14" t="inlineStr">
-        <is>
-          <t>사용자별 알림 수신 설정을 따르며 미설정 시 발송하지 않는다.</t>
-        </is>
-      </c>
-      <c r="J106" s="14" t="inlineStr">
-        <is>
-          <t>W12 피드백 · 마이페이지</t>
-        </is>
-      </c>
-      <c r="K106" s="14" t="inlineStr">
         <is>
           <t>초안</t>
         </is>

--- a/docs/요구사항_정의서_파이온_최종.xlsx
+++ b/docs/요구사항_정의서_파이온_최종.xlsx
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1835,6 +1835,43 @@
       <c r="G17" s="27" t="inlineStr">
         <is>
           <t>요구사항 자체는 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>v1.7</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>REQ-RECO-001(LLM 예방행동 제안)·REQ-NOTI-003(LLM 추천 알림) 존재</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>두 요구사항 삭제, LLM 전제 문구 정리</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — AI 추천 기능을 하지 않기로 함</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="inlineStr">
+        <is>
+          <t>식단 사진 분석(REQ-RECO-002)은 추천이 아니라 분석이라 유지</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.00500011" customWidth="1" min="1" max="1"/>
@@ -4565,6 +4602,90 @@
         </is>
       </c>
       <c r="F85" s="27" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="27" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+      <c r="B86" s="27" t="inlineStr">
+        <is>
+          <t>REQ-NOTI-003</t>
+        </is>
+      </c>
+      <c r="C86" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D86" s="27" t="inlineStr">
+        <is>
+          <t>AI 추천 관련 요구사항</t>
+        </is>
+      </c>
+      <c r="E86" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — AI 추천 미도입</t>
+        </is>
+      </c>
+      <c r="F86" s="27" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="27" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+      <c r="B87" s="27" t="inlineStr">
+        <is>
+          <t>REQ-RECO-001</t>
+        </is>
+      </c>
+      <c r="C87" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D87" s="27" t="inlineStr">
+        <is>
+          <t>AI 추천 관련 요구사항</t>
+        </is>
+      </c>
+      <c r="E87" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — AI 추천 미도입</t>
+        </is>
+      </c>
+      <c r="F87" s="27" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-002</t>
+        </is>
+      </c>
+      <c r="C88" s="27" t="inlineStr">
+        <is>
+          <t>안전성</t>
+        </is>
+      </c>
+      <c r="D88" s="27" t="inlineStr">
+        <is>
+          <t>LLM 전제 문구를 일반 안내 문구로 조정</t>
+        </is>
+      </c>
+      <c r="E88" s="27" t="inlineStr">
+        <is>
+          <t>AI 추천 미도입에 맞춤</t>
+        </is>
+      </c>
+      <c r="F88" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4578,7 +4699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.00500011" customWidth="1" min="1" max="1"/>
@@ -7389,228 +7510,228 @@
       </c>
     </row>
     <row r="50" ht="40.5" customHeight="1">
-      <c r="A50" s="22" t="inlineStr">
-        <is>
-          <t>REQ-RECO-001</t>
-        </is>
-      </c>
-      <c r="B50" s="23" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>REQ-RECO-002</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>추천</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
-        <is>
-          <t>LLM 생성</t>
-        </is>
-      </c>
-      <c r="D50" s="23" t="inlineStr">
-        <is>
-          <t>근거 기반</t>
-        </is>
-      </c>
-      <c r="E50" s="23" t="inlineStr">
-        <is>
-          <t>행동 제안</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="inlineStr">
-        <is>
-          <t>사용자는 예측 결과와 승인된 건강정보를 근거로 생성된 예방 행동 제안을 확인할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G50" s="23" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>식단 분석</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>나트륨 점수화</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>이미지 인식</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>사용자는 식단 사진을 올려 나트륨 중심의 점수와 개선 제안을 확인할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H50" s="23" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="I50" s="23" t="inlineStr">
-        <is>
-          <t>제안마다 생성 시각을 표시. 약물·처방 관련 제안 금지.</t>
-        </is>
-      </c>
-      <c r="J50" s="23" t="inlineStr">
-        <is>
-          <t>W06 예측 결과 · XAI 설명</t>
-        </is>
-      </c>
-      <c r="K50" s="23" t="inlineStr">
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>점수 기준은 칼로리가 아닌 나트륨. 음식별 영양소는 식약처 공개 데이터를 기준으로 한다. 분석 실패 시 직접 입력으로 대체 가능.</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>W10 챌린지 수행 · 인증</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="51" ht="27" customHeight="1">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>REQ-RECO-002</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>추천</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>식단 분석</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>나트륨 점수화</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>이미지 인식</t>
-        </is>
-      </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>사용자는 식단 사진을 올려 나트륨 중심의 점수와 개선 제안을 확인할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G51" s="11" t="inlineStr">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>REQ-NOTI-001</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>리마인더</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>시작 알림</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>발송 시각</t>
+        </is>
+      </c>
+      <c r="F51" s="19" t="inlineStr">
+        <is>
+          <t>사용자는 아침 지정 시각에 그날의 챌린지 시작 알림을 받을 수 있어야 한다. 문구는 참여를 강요하지 않는 톤으로 한다.</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H51" s="11" t="inlineStr">
+      <c r="H51" s="19" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>점수 기준은 칼로리가 아닌 나트륨. 음식별 영양소는 식약처 공개 데이터를 기준으로 한다. 분석 실패 시 직접 입력으로 대체 가능.</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="inlineStr">
-        <is>
-          <t>W10 챌린지 수행 · 인증</t>
-        </is>
-      </c>
-      <c r="K51" s="11" t="inlineStr">
+      <c r="I51" s="19" t="inlineStr">
+        <is>
+          <t>사용자별 수신 설정을 따르며 미설정 시 발송하지 않는다. 발송 시각은 사용자가 바꿀 수 있다. 웹 푸시는 HTTPS와 사용자 동작으로 받은 권한이 있을 때만 발송한다. 알림 설정과 개인정보 안내를 같은 화면에서 확인할 수 있게 한다. (PRD CH-09)</t>
+        </is>
+      </c>
+      <c r="J51" s="19" t="inlineStr">
+        <is>
+          <t>W12 피드백 · 마이페이지</t>
+        </is>
+      </c>
+      <c r="K51" s="19" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="52" ht="27" customHeight="1">
-      <c r="A52" s="18" t="inlineStr">
-        <is>
-          <t>REQ-NOTI-001</t>
-        </is>
-      </c>
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>알림</t>
-        </is>
-      </c>
-      <c r="C52" s="19" t="inlineStr">
-        <is>
-          <t>리마인더</t>
-        </is>
-      </c>
-      <c r="D52" s="19" t="inlineStr">
-        <is>
-          <t>시작 알림</t>
-        </is>
-      </c>
-      <c r="E52" s="19" t="inlineStr">
-        <is>
-          <t>발송 시각</t>
-        </is>
-      </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t>사용자는 아침 지정 시각에 그날의 챌린지 시작 알림을 받을 수 있어야 한다. 문구는 참여를 강요하지 않는 톤으로 한다.</t>
-        </is>
-      </c>
-      <c r="G52" s="19" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>REQ-FEED-001</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>결과·추천</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>의견 수집</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>저장</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>사용자는 예측 결과와 추천에 대한 평가와 의견을 남길 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H52" s="19" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="I52" s="19" t="inlineStr">
-        <is>
-          <t>사용자별 수신 설정을 따르며 미설정 시 발송하지 않는다. 발송 시각은 사용자가 바꿀 수 있다. 웹 푸시는 HTTPS와 사용자 동작으로 받은 권한이 있을 때만 발송한다. 알림 설정과 개인정보 안내를 같은 화면에서 확인할 수 있게 한다. (PRD CH-09)</t>
-        </is>
-      </c>
-      <c r="J52" s="19" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>평가 대상(예측/추천)과 대상 버전을 함께 저장.</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>W12 피드백 · 마이페이지</t>
         </is>
       </c>
-      <c r="K52" s="19" t="inlineStr">
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40.5" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>REQ-FEED-001</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>REQ-FEED-002</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>피드백</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>결과·추천</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>의견 수집</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>저장</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>사용자는 예측 결과와 추천에 대한 평가와 의견을 남길 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>난이도</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>사이클 종료 평가</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>사용자는 사이클 종료 시 수행한 챌린지의 난이도를 평가할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" s="9" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>평가 대상(예측/추천)과 대상 버전을 함께 저장.</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>W12 피드백 · 마이페이지</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>쉬움·적당·어려움 3단계로 저장. 다음 사이클 난이도 추천에 반영되는 것을 확인.</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>W11 추이 · 변화 추적</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -7619,7 +7740,7 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>REQ-FEED-002</t>
+          <t>REQ-FEED-003</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
@@ -7629,22 +7750,22 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>챌린지</t>
+          <t>추천</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>난이도</t>
+          <t>거절 사유</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>사이클 종료 평가</t>
+          <t>선택적 수집</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>사용자는 사이클 종료 시 수행한 챌린지의 난이도를 평가할 수 있어야 한다.</t>
+          <t>추천한 챌린지를 선택하지 않은 경우 사유를 선택적으로 수집할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -7654,248 +7775,248 @@
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>"이미 하고 있음 / 관심 없음 / 실천이 어려움" 중 선택. 응답은 선택 사항.</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>W09 챌린지 선택</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="27" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>NFR-FEED-001</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>개선</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>분석</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>활용 이력</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>수집한 피드백은 분석 리포트와 개선 후보로 연결되어야 한다.</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>쉬움·적당·어려움 3단계로 저장. 다음 사이클 난이도 추천에 반영되는 것을 확인.</t>
-        </is>
-      </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t>W11 추이 · 변화 추적</t>
-        </is>
-      </c>
-      <c r="K54" s="9" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>피드백 통계와 개선 반영 이력을 제출.</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="27" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>REQ-FEED-003</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
+    <row r="56" ht="27" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>NFR-FEED-002</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>피드백</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>추천</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>거절 사유</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>선택적 수집</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>추천한 챌린지를 선택하지 않은 경우 사유를 선택적으로 수집할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>"이미 하고 있음 / 관심 없음 / 실천이 어려움" 중 선택. 응답은 선택 사항.</t>
-        </is>
-      </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>W09 챌린지 선택</t>
-        </is>
-      </c>
-      <c r="K55" s="9" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>설문</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>파생 가중치</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>보정 가능</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>설문 응답에서 파생 피처를 만들 때 쓰는 가중치는 피드백과 실측 데이터로 보정할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>가중치를 코드가 아닌 설정으로 관리하고 변경 이력을 남긴다.</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="27" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>NFR-FEED-001</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>피드백</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>개선</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>분석</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>활용 이력</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>수집한 피드백은 분석 리포트와 개선 후보로 연결되어야 한다.</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-001</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>안전성</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>결과 표현</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>위험 선별</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>면책 안내</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>모든 예측 결과 화면에 진단이 아닌 선별 정보라는 면책 문구를 표시해야 한다.</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>피드백 통계와 개선 반영 이력을 제출.</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>결과가 표시되는 모든 화면·API 응답에 면책 문구 포함.</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>W06 예측 결과 · XAI 설명, W07 검사 · 상담 안내, W08 대시보드 (홈)</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>NFR-FEED-002</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>피드백</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>설문</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>파생 가중치</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>보정 가능</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>설문 응답에서 파생 피처를 만들 때 쓰는 가중치는 피드백과 실측 데이터로 보정할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
+    <row r="58" ht="27" customHeight="1">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-002</t>
+        </is>
+      </c>
+      <c r="B58" s="23" t="inlineStr">
+        <is>
+          <t>안전성</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>금지 행동</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="inlineStr">
+        <is>
+          <t>약물</t>
+        </is>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
+        <is>
+          <t>처방 제한</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>서비스는 약물 복용·변경·중단을 권고하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>가중치를 코드가 아닌 설정으로 관리하고 변경 이력을 남긴다.</t>
-        </is>
-      </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K57" s="9" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="27" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>NFR-SAFE-001</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>안전성</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>결과 표현</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>위험 선별</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>면책 안내</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>모든 예측 결과 화면에 진단이 아닌 선별 정보라는 면책 문구를 표시해야 한다.</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H58" s="23" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>결과가 표시되는 모든 화면·API 응답에 면책 문구 포함.</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>W06 예측 결과 · XAI 설명, W07 검사 · 상담 안내, W08 대시보드 (홈)</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="I58" s="23" t="inlineStr">
+        <is>
+          <t>자동 생성되는 안내 문구에 안전 필터를 적용한다. 약물·처방 관련 질의는 의료기관 문의로 안내한다.</t>
+        </is>
+      </c>
+      <c r="J58" s="23" t="inlineStr">
+        <is>
+          <t>W06 예측 결과 · XAI 설명</t>
+        </is>
+      </c>
+      <c r="K58" s="23" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -7904,7 +8025,7 @@
     <row r="59" ht="40.5" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>NFR-SAFE-002</t>
+          <t>NFR-SAFE-003</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -7914,22 +8035,22 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>금지 행동</t>
+          <t>설명</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>약물</t>
+          <t>불확실성</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>처방 제한</t>
+          <t>과도한 확신 방지</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>서비스는 약물 복용·변경·중단을 권고하지 않는다.</t>
+          <t>예측 결과를 확정 발병 확률로 표현하지 않는다.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -7944,7 +8065,7 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>LLM 응답에 안전 필터 적용. 금지 질의는 의료기관 문의로 안내.</t>
+          <t>확률 단정 표현 금지. 범주형 위험 신호로 표시.</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
@@ -7959,171 +8080,171 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>NFR-SAFE-003</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-004</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>안전성</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>불확실성</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>과도한 확신 방지</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>예측 결과를 확정 발병 확률로 표현하지 않는다.</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>응급</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>선별</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>즉시 안내</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>응급 의심 증상을 선택한 사용자에게는 예측을 진행하지 않고 즉시 응급 연락 안내를 표시한다.</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H60" s="9" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>확률 단정 표현 금지. 범주형 위험 신호로 표시.</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>W06 예측 결과 · XAI 설명</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>응급 문진 양성 시 입력·예측 화면 진입을 막고 안내만 노출(REQ-ELIG-003 연계).</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>W03 이용 적합성 · 응급 확인</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="61" ht="27" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>NFR-SAFE-004</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-005</t>
+        </is>
+      </c>
+      <c r="B61" s="23" t="inlineStr">
         <is>
           <t>안전성</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>응급</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>선별</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>즉시 안내</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>응급 의심 증상을 선택한 사용자에게는 예측을 진행하지 않고 즉시 응급 연락 안내를 표시한다.</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
+      <c r="C61" s="23" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="inlineStr">
+        <is>
+          <t>잠정값</t>
+        </is>
+      </c>
+      <c r="E61" s="23" t="inlineStr">
+        <is>
+          <t>고지</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="inlineStr">
+        <is>
+          <t>학습 데이터가 확정되기 전의 잠정 모델을 사용하는 동안에는 결과 화면에 그 사실을 고지해야 한다.</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H61" s="9" t="inlineStr">
+      <c r="H61" s="23" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>응급 문진 양성 시 입력·예측 화면 진입을 막고 안내만 노출(REQ-ELIG-003 연계).</t>
-        </is>
-      </c>
-      <c r="J61" s="9" t="inlineStr">
-        <is>
-          <t>W03 이용 적합성 · 응급 확인</t>
-        </is>
-      </c>
-      <c r="K61" s="9" t="inlineStr">
+      <c r="I61" s="23" t="inlineStr">
+        <is>
+          <t>결과 화면에 모델의 확정 여부를 표기한다. 확정 후 문구를 제거하는 절차를 정의한다.</t>
+        </is>
+      </c>
+      <c r="J61" s="23" t="inlineStr">
+        <is>
+          <t>W06 예측 결과 · XAI 설명, W08 대시보드 (홈), W11 추이 · 변화 추적</t>
+        </is>
+      </c>
+      <c r="K61" s="23" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="62" ht="27" customHeight="1">
-      <c r="A62" s="22" t="inlineStr">
-        <is>
-          <t>NFR-SAFE-005</t>
-        </is>
-      </c>
-      <c r="B62" s="23" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>NFR-SAFE-006</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>안전성</t>
         </is>
       </c>
-      <c r="C62" s="23" t="inlineStr">
-        <is>
-          <t>모델</t>
-        </is>
-      </c>
-      <c r="D62" s="23" t="inlineStr">
-        <is>
-          <t>잠정값</t>
-        </is>
-      </c>
-      <c r="E62" s="23" t="inlineStr">
-        <is>
-          <t>고지</t>
-        </is>
-      </c>
-      <c r="F62" s="23" t="inlineStr">
-        <is>
-          <t>학습 데이터가 확정되기 전의 잠정 모델을 사용하는 동안에는 결과 화면에 그 사실을 고지해야 한다.</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>톤</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>상업적 표현</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>금지</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>예측·챌린지 화면에 이벤트성 배너, 광고, 제휴 콘텐츠를 노출하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H62" s="23" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="I62" s="23" t="inlineStr">
-        <is>
-          <t>결과 화면에 모델의 확정 여부를 표기한다. 확정 후 문구를 제거하는 절차를 정의한다.</t>
-        </is>
-      </c>
-      <c r="J62" s="23" t="inlineStr">
-        <is>
-          <t>W06 예측 결과 · XAI 설명, W08 대시보드 (홈), W11 추이 · 변화 추적</t>
-        </is>
-      </c>
-      <c r="K62" s="23" t="inlineStr">
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>해당 영역은 자체 생성 콘텐츠로만 채운다. 외부 제휴 링크 미존재.</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>전 화면</t>
+        </is>
+      </c>
+      <c r="K62" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -8132,7 +8253,7 @@
     <row r="63" ht="40.5" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>NFR-SAFE-006</t>
+          <t>NFR-SAFE-007</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -8142,22 +8263,22 @@
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>톤</t>
+          <t>추천</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>상업적 표현</t>
+          <t>복약</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>금지</t>
+          <t>중단 유도 금지</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>예측·챌린지 화면에 이벤트성 배너, 광고, 제휴 콘텐츠를 노출하지 않는다.</t>
+          <t>고혈압 약을 복용 중이라고 응답한 사용자에게 복약 중단·감량을 시사하는 문구를 노출하지 않는다.</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr">
@@ -8167,17 +8288,17 @@
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>해당 영역은 자체 생성 콘텐츠로만 채운다. 외부 제휴 링크 미존재.</t>
+          <t>복약 응답자에게는 생활습관 개선 문구만 제시(NFR-SAFE-002 연계).</t>
         </is>
       </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>전 화면</t>
+          <t>W06 예측 결과 · XAI 설명, W09 챌린지 선택</t>
         </is>
       </c>
       <c r="K63" s="9" t="inlineStr">
@@ -8187,57 +8308,57 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>NFR-SAFE-007</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>안전성</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>추천</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>복약</t>
-        </is>
-      </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>중단 유도 금지</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="inlineStr">
-        <is>
-          <t>고혈압 약을 복용 중이라고 응답한 사용자에게 복약 중단·감량을 시사하는 문구를 노출하지 않는다.</t>
-        </is>
-      </c>
-      <c r="G64" s="9" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>NFR-SEC-001</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>보안</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>비밀번호</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>해시 저장</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>비밀번호는 검증 가능한 해시로 저장해야 한다.</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H64" s="9" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>복약 응답자에게는 생활습관 개선 문구만 제시(NFR-SAFE-002 연계).</t>
-        </is>
-      </c>
-      <c r="J64" s="9" t="inlineStr">
-        <is>
-          <t>W06 예측 결과 · XAI 설명, W09 챌린지 선택</t>
-        </is>
-      </c>
-      <c r="K64" s="9" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>평문·가역 암호화 저장 금지.</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -8246,7 +8367,7 @@
     <row r="65" ht="27" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>NFR-SEC-001</t>
+          <t>NFR-SEC-002</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -8256,22 +8377,22 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>인증</t>
+          <t>권한</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>비밀번호</t>
+          <t>소유권</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>해시 저장</t>
+          <t>접근 통제</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>비밀번호는 검증 가능한 해시로 저장해야 한다.</t>
+          <t>개인 API는 JWT를 검증하고 자원 소유자 본인만 접근할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -8286,7 +8407,7 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>평문·가역 암호화 저장 금지.</t>
+          <t>타 사용자 자원 접근 시 403. 토큰 없음·만료 401.</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
@@ -8303,7 +8424,7 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>NFR-SEC-002</t>
+          <t>NFR-SEC-003</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
@@ -8313,22 +8434,22 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>권한</t>
+          <t>수집</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>소유권</t>
+          <t>최소화</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>접근 통제</t>
+          <t>목적 제한</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>개인 API는 JWT를 검증하고 자원 소유자 본인만 접근할 수 있어야 한다.</t>
+          <t>서비스 목적에 필요한 최소 건강정보만 수집한다.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -8343,12 +8464,12 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>타 사용자 자원 접근 시 403. 토큰 없음·만료 401.</t>
+          <t>수집 항목별 목적을 동의서에 명시.</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>W02 회원가입 · 로그인 · 동의, W04 건강정보 입력</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
@@ -8360,7 +8481,7 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>NFR-SEC-003</t>
+          <t>NFR-SEC-004</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -8370,22 +8491,22 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>수집</t>
+          <t>로그</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>최소화</t>
+          <t>민감정보</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>목적 제한</t>
+          <t>마스킹</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>서비스 목적에 필요한 최소 건강정보만 수집한다.</t>
+          <t>로그와 URL에 건강정보·식별정보를 포함하지 않는다.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -8400,12 +8521,12 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>수집 항목별 목적을 동의서에 명시.</t>
+          <t>민감 필드는 마스킹 후 기록. URL 쿼리에 건강정보 금지.</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>W02 회원가입 · 로그인 · 동의, W04 건강정보 입력</t>
+          <t>해당 없음</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -8415,57 +8536,57 @@
       </c>
     </row>
     <row r="68" ht="27" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>NFR-SEC-004</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>NFR-SEC-005</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>보안</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>로그</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>민감정보</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>마스킹</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>로그와 URL에 건강정보·식별정보를 포함하지 않는다.</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>검진 결과지</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>보관 최소화</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>검진 결과지 업로드 이미지는 값 추출 처리 후 지체 없이 삭제하고 추출된 수치만 저장한다.</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="H68" s="9" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>민감 필드는 마스킹 후 기록. URL 쿼리에 건강정보 금지.</t>
-        </is>
-      </c>
-      <c r="J68" s="5" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K68" s="5" t="inlineStr">
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>원본 이미지 보관 기간을 동의서에 명시. 처리 후 삭제 사실을 로그로 확인.</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>W04 건강정보 입력</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -8474,7 +8595,7 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>NFR-SEC-005</t>
+          <t>NFR-SEC-006</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -8484,22 +8605,22 @@
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>이미지</t>
+          <t>수집</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>검진 결과지</t>
+          <t>설문 응답</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>보관 최소화</t>
+          <t>건강정보 취급</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>검진 결과지 업로드 이미지는 값 추출 처리 후 지체 없이 삭제하고 추출된 수치만 저장한다.</t>
+          <t>생활습관 설문 응답도 건강정보로 분류해 동일한 보호 조치를 적용한다.</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
@@ -8514,12 +8635,12 @@
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>원본 이미지 보관 기간을 동의서에 명시. 처리 후 삭제 사실을 로그로 확인.</t>
+          <t>설문 항목을 동의서 수집 항목에 포함. 암호화·접근통제 대상에 포함(NFR-SEC-002, 003 연계).</t>
         </is>
       </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>W04 건강정보 입력</t>
+          <t>W02 회원가입 · 로그인 · 동의, W04 건강정보 입력</t>
         </is>
       </c>
       <c r="K69" s="9" t="inlineStr">
@@ -8531,7 +8652,7 @@
     <row r="70" ht="27" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>NFR-SEC-006</t>
+          <t>NFR-SEC-007</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -8541,22 +8662,22 @@
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>수집</t>
+          <t>목적 제한</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>설문 응답</t>
+          <t>외부 제공</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>건강정보 취급</t>
+          <t>금지·고지</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>생활습관 설문 응답도 건강정보로 분류해 동일한 보호 조치를 적용한다.</t>
+          <t>수집한 건강정보를 서비스 목적 외로 이용하거나 제3자에게 제공하지 않으며, 그 사실을 입력 화면에 명시한다.</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
@@ -8571,12 +8692,12 @@
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>설문 항목을 동의서 수집 항목에 포함. 암호화·접근통제 대상에 포함(NFR-SEC-002, 003 연계).</t>
+          <t>입력 화면에 고지 문구를 노출하고, 외부 전송 경로가 없음을 코드로 증빙.</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>W02 회원가입 · 로그인 · 동의, W04 건강정보 입력</t>
+          <t>W04 건강정보 입력</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
@@ -8586,57 +8707,57 @@
       </c>
     </row>
     <row r="71" ht="27" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>NFR-SEC-007</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>목적 제한</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>외부 제공</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>금지·고지</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>수집한 건강정보를 서비스 목적 외로 이용하거나 제3자에게 제공하지 않으며, 그 사실을 입력 화면에 명시한다.</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>NFR-ACC-001</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>접근성</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>시각</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>글자·대비</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>고령자 지원</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>본문 텍스트 대비와 최소 글자 크기 기준을 충족해야 한다.</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H71" s="9" t="inlineStr">
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>입력 화면에 고지 문구를 노출하고, 외부 전송 경로가 없음을 코드로 증빙.</t>
-        </is>
-      </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>W04 건강정보 입력</t>
-        </is>
-      </c>
-      <c r="K71" s="9" t="inlineStr">
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>본문 대비 4.5:1 이상. 본문 최소 16px.</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>전 화면</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -8645,7 +8766,7 @@
     <row r="72" ht="27" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>NFR-ACC-001</t>
+          <t>NFR-ACC-002</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -8655,22 +8776,22 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>시각</t>
+          <t>조작</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>글자·대비</t>
+          <t>터치 영역</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>고령자 지원</t>
+          <t>오입력 방지</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>본문 텍스트 대비와 최소 글자 크기 기준을 충족해야 한다.</t>
+          <t>주요 터치 대상은 충분한 크기를 확보해야 한다.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -8680,12 +8801,12 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>본문 대비 4.5:1 이상. 본문 최소 16px.</t>
+          <t>터치 대상 최소 44x44px.</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
@@ -8702,7 +8823,7 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>NFR-ACC-002</t>
+          <t>NFR-ACC-003</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
@@ -8712,22 +8833,22 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>조작</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>터치 영역</t>
+          <t>비색상 정보</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>오입력 방지</t>
+          <t>중복 표현</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>주요 터치 대상은 충분한 크기를 확보해야 한다.</t>
+          <t>상태를 색상만으로 구분하지 않는다.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -8737,12 +8858,12 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>터치 대상 최소 44x44px.</t>
+          <t>색상 + 아이콘 또는 텍스트를 함께 제공.</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
@@ -8759,7 +8880,7 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>NFR-ACC-003</t>
+          <t>NFR-ACC-004</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
@@ -8769,22 +8890,22 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>키보드·보조기술</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>비색상 정보</t>
+          <t>폼</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>중복 표현</t>
+          <t>레이블·초점</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>상태를 색상만으로 구분하지 않는다.</t>
+          <t>모든 입력 요소에 레이블을 연결하고 키보드로 조작할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -8794,12 +8915,12 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>색상 + 아이콘 또는 텍스트를 함께 제공.</t>
+          <t>탭 순서가 시각적 순서와 일치. 초점 표시 유지.</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
@@ -8816,32 +8937,32 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>NFR-ACC-004</t>
+          <t>NFR-UX-001</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>접근성</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>키보드·보조기술</t>
+          <t>탐색</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>폼</t>
+          <t>핵심 기능</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>레이블·초점</t>
+          <t>3~5회 액션</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>모든 입력 요소에 레이블을 연결하고 키보드로 조작할 수 있어야 한다.</t>
+          <t>핵심 기능은 홈에서 3~5회 이내 액션으로 도달할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -8851,12 +8972,12 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>중간</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>탭 순서가 시각적 순서와 일치. 초점 표시 유지.</t>
+          <t>핵심 기능별 액션 수 표를 작성해 증빙.</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
@@ -8873,7 +8994,7 @@
     <row r="76" ht="27" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>NFR-UX-001</t>
+          <t>NFR-UX-002</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -8883,22 +9004,22 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>탐색</t>
+          <t>일관성</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>핵심 기능</t>
+          <t>디자인 시스템</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>3~5회 액션</t>
+          <t>공통 패턴</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>핵심 기능은 홈에서 3~5회 이내 액션으로 도달할 수 있어야 한다.</t>
+          <t>버튼·폼·카드·알림은 공통 컴포넌트를 사용해야 한다.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -8913,7 +9034,7 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>핵심 기능별 액션 수 표를 작성해 증빙.</t>
+          <t>공통 컴포넌트 목록과 사용 화면 매핑을 유지.</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
@@ -8930,32 +9051,32 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>NFR-UX-002</t>
+          <t>NFR-API-001</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>API</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>HTTP Method·URI</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
           <t>일관성</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>디자인 시스템</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>공통 패턴</t>
-        </is>
-      </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>버튼·폼·카드·알림은 공통 컴포넌트를 사용해야 한다.</t>
+          <t>API는 자원 중심 URI와 목적에 맞는 HTTP Method를 사용해야 한다.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -8970,12 +9091,12 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>공통 컴포넌트 목록과 사용 화면 매핑을 유지.</t>
+          <t>조회 GET, 생성 POST, 전체수정 PUT, 부분수정 PATCH, 삭제 DELETE.</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>전 화면</t>
+          <t>해당 없음</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
@@ -8987,7 +9108,7 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>NFR-API-001</t>
+          <t>NFR-API-002</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -8997,22 +9118,22 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>성능</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>HTTP Method·URI</t>
+          <t>전체 API</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>일관성</t>
+          <t>P95 3초</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>API는 자원 중심 URI와 목적에 맞는 HTTP Method를 사용해야 한다.</t>
+          <t>전체 API 응답시간 P95는 3초 이내여야 한다.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -9027,7 +9148,7 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>조회 GET, 생성 POST, 전체수정 PUT, 부분수정 PATCH, 삭제 DELETE.</t>
+          <t>부하 테스트 결과로 증빙. 초과 API는 원인과 개선안을 기록.</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
@@ -9044,32 +9165,32 @@
     <row r="79" ht="27" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>NFR-API-002</t>
+          <t>NFR-ASYNC-001</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>비동기</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>성능</t>
+          <t>AI 추론</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>전체 API</t>
+          <t>작업 큐</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>P95 3초</t>
+          <t>비동기 실행</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>전체 API 응답시간 P95는 3초 이내여야 한다.</t>
+          <t>AI 추론은 작업 큐를 통해 비동기로 실행되어야 한다.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -9084,12 +9205,12 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>부하 테스트 결과로 증빙. 초과 API는 원인과 개선안을 기록.</t>
+          <t>동기 방식 대비 처리량·응답시간 차이를 수치로 제시.</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>W05 입력 검토 · 분석 대기</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
@@ -9101,7 +9222,7 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>NFR-ASYNC-001</t>
+          <t>NFR-ASYNC-002</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -9111,22 +9232,22 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>AI 추론</t>
+          <t>서버 I/O</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>작업 큐</t>
+          <t>DB·외부 API</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>비동기 실행</t>
+          <t>async 처리</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>AI 추론은 작업 큐를 통해 비동기로 실행되어야 한다.</t>
+          <t>DB와 외부 API 호출은 async I/O로 처리해야 한다.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -9141,12 +9262,12 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>동기 방식 대비 처리량·응답시간 차이를 수치로 제시.</t>
+          <t>블로킹 호출이 이벤트 루프를 점유하지 않음을 확인.</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>W05 입력 검토 · 분석 대기</t>
+          <t>해당 없음</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
@@ -9156,228 +9277,228 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>NFR-ASYNC-002</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>비동기</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>서버 I/O</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>DB·외부 API</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>async 처리</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>DB와 외부 API 호출은 async I/O로 처리해야 한다.</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="A81" s="20" t="inlineStr">
+        <is>
+          <t>NFR-ML-001</t>
+        </is>
+      </c>
+      <c r="B81" s="21" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="inlineStr">
+        <is>
+          <t>데이터 분리</t>
+        </is>
+      </c>
+      <c r="D81" s="21" t="inlineStr">
+        <is>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="E81" s="21" t="inlineStr">
+        <is>
+          <t>누수 방지</t>
+        </is>
+      </c>
+      <c r="F81" s="21" t="inlineStr">
+        <is>
+          <t>학습·검증·테스트를 분리하고 전처리는 학습 데이터 기준으로 적합시켜야 한다.</t>
+        </is>
+      </c>
+      <c r="G81" s="21" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="H81" s="21" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>블로킹 호출이 이벤트 루프를 점유하지 않음을 확인.</t>
-        </is>
-      </c>
-      <c r="J81" s="5" t="inlineStr">
+      <c r="I81" s="21" t="inlineStr">
+        <is>
+          <t>스케일러·인코더를 학습 셋에만 fit. 분리 코드로 증빙. 결측 코드는 변수별 의미에 따라 구분 처리한다(예: 8=비해당·해당 범주 유지, 9=모름/무응답만 결측 처리) — 임의로 통합 처리하지 않는다.</t>
+        </is>
+      </c>
+      <c r="J81" s="21" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K81" s="5" t="inlineStr">
+      <c r="K81" s="21" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>NFR-ML-001</t>
-        </is>
-      </c>
-      <c r="B82" s="21" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>NFR-ML-002</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>모델</t>
         </is>
       </c>
-      <c r="C82" s="21" t="inlineStr">
-        <is>
-          <t>데이터 분리</t>
-        </is>
-      </c>
-      <c r="D82" s="21" t="inlineStr">
-        <is>
-          <t>전처리</t>
-        </is>
-      </c>
-      <c r="E82" s="21" t="inlineStr">
-        <is>
-          <t>누수 방지</t>
-        </is>
-      </c>
-      <c r="F82" s="21" t="inlineStr">
-        <is>
-          <t>학습·검증·테스트를 분리하고 전처리는 학습 데이터 기준으로 적합시켜야 한다.</t>
-        </is>
-      </c>
-      <c r="G82" s="21" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>특징</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>라벨 누수</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>타깃 정보가 새는 특징을 학습에 사용하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H82" s="21" t="inlineStr">
+      <c r="H82" s="5" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I82" s="21" t="inlineStr">
-        <is>
-          <t>스케일러·인코더를 학습 셋에만 fit. 분리 코드로 증빙. 결측 코드는 변수별 의미에 따라 구분 처리한다(예: 8=비해당·해당 범주 유지, 9=모름/무응답만 결측 처리) — 임의로 통합 처리하지 않는다.</t>
-        </is>
-      </c>
-      <c r="J82" s="21" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>특징별 누수 검토 결과를 기록.</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K82" s="21" t="inlineStr">
+      <c r="K82" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="83" ht="27" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>NFR-ML-002</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="A83" s="20" t="inlineStr">
+        <is>
+          <t>NFR-ML-003</t>
+        </is>
+      </c>
+      <c r="B83" s="21" t="inlineStr">
         <is>
           <t>모델</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>라벨 누수</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>검토</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>타깃 정보가 새는 특징을 학습에 사용하지 않는다.</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="C83" s="21" t="inlineStr">
+        <is>
+          <t>평가</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>분류 지표</t>
+        </is>
+      </c>
+      <c r="E83" s="21" t="inlineStr">
+        <is>
+          <t>비교</t>
+        </is>
+      </c>
+      <c r="F83" s="21" t="inlineStr">
+        <is>
+          <t>2개 이상 모델을 동일 조건에서 비교하고 지표를 기록해야 한다.</t>
+        </is>
+      </c>
+      <c r="G83" s="21" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H83" s="21" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>특징별 누수 검토 결과를 기록.</t>
-        </is>
-      </c>
-      <c r="J83" s="5" t="inlineStr">
+      <c r="I83" s="21" t="inlineStr">
+        <is>
+          <t>평가지표는 AUC-ROC를 기본으로 하고 F1-score·혼동행렬을 함께 기록한다. 로지스틱회귀(베이스라인)와 트리 계열 모델(XGBoost 또는 LightGBM) 최소 2종을 동일 조건에서 비교한다. 실험표·혼동행렬·개선 전후 결과를 제출.</t>
+        </is>
+      </c>
+      <c r="J83" s="21" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K83" s="5" t="inlineStr">
+      <c r="K83" s="21" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>NFR-ML-003</t>
-        </is>
-      </c>
-      <c r="B84" s="21" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>NFR-ML-004</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>모델</t>
         </is>
       </c>
-      <c r="C84" s="21" t="inlineStr">
-        <is>
-          <t>평가</t>
-        </is>
-      </c>
-      <c r="D84" s="21" t="inlineStr">
-        <is>
-          <t>분류 지표</t>
-        </is>
-      </c>
-      <c r="E84" s="21" t="inlineStr">
-        <is>
-          <t>비교</t>
-        </is>
-      </c>
-      <c r="F84" s="21" t="inlineStr">
-        <is>
-          <t>2개 이상 모델을 동일 조건에서 비교하고 지표를 기록해야 한다.</t>
-        </is>
-      </c>
-      <c r="G84" s="21" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>재현성</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>버전</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>모델·전처리·임계값 버전을 예측 결과와 함께 저장해야 한다.</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H84" s="21" t="inlineStr">
+      <c r="H84" s="5" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I84" s="21" t="inlineStr">
-        <is>
-          <t>평가지표는 AUC-ROC를 기본으로 하고 F1-score·혼동행렬을 함께 기록한다. 로지스틱회귀(베이스라인)와 트리 계열 모델(XGBoost 또는 LightGBM) 최소 2종을 동일 조건에서 비교한다. 실험표·혼동행렬·개선 전후 결과를 제출.</t>
-        </is>
-      </c>
-      <c r="J84" s="21" t="inlineStr">
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>예측 레코드에서 사용된 모델 버전을 역추적할 수 있다.</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K84" s="21" t="inlineStr">
+      <c r="K84" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -9386,7 +9507,7 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>NFR-ML-004</t>
+          <t>NFR-ML-005</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
@@ -9396,22 +9517,22 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>재현성</t>
+          <t>일관성</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>버전</t>
+          <t>동일 입력</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>반복 검증</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>모델·전처리·임계값 버전을 예측 결과와 함께 저장해야 한다.</t>
+          <t>동일 입력에 대해 반복 예측 시 결과가 일치해야 한다.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -9426,7 +9547,7 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>예측 레코드에서 사용된 모델 버전을 역추적할 수 있다.</t>
+          <t>100건 x 10회 반복 테스트에서 점수 편차 0.</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
@@ -9441,114 +9562,114 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>NFR-ML-005</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>NFR-ML-006</t>
+        </is>
+      </c>
+      <c r="B86" s="21" t="inlineStr">
         <is>
           <t>모델</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>일관성</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>동일 입력</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>반복 검증</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>동일 입력에 대해 반복 예측 시 결과가 일치해야 한다.</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="C86" s="21" t="inlineStr">
+        <is>
+          <t>재학습</t>
+        </is>
+      </c>
+      <c r="D86" s="21" t="inlineStr">
+        <is>
+          <t>누적 데이터</t>
+        </is>
+      </c>
+      <c r="E86" s="21" t="inlineStr">
+        <is>
+          <t>주기</t>
+        </is>
+      </c>
+      <c r="F86" s="21" t="inlineStr">
+        <is>
+          <t>챌린지 후보로 채택되는 생활습관 피처는 학습 데이터에서 라벨과의 상관관계 또는 유의미한 영향력이 사전에 검증된 것이어야 한다.</t>
+        </is>
+      </c>
+      <c r="G86" s="21" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="H86" s="21" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I86" s="21" t="inlineStr">
+        <is>
+          <t>피처별 SHAP 중요도 평균(절댓값) 상위 5위 이내이거나, 라벨과의 상관계수 절댓값이 0.1 이상인 피처만 챌린지 후보로 채택한다. 기준 미달 피처는 챌린지 후보에서 제외하거나 참고용으로만 표시한다. 분석 결과는 REQ-CHAL의 고정·선택 미션 분류 근거로 사용한다.</t>
+        </is>
+      </c>
+      <c r="J86" s="21" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K86" s="21" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>NFR-ARCH-001</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>아키텍처</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>계층 분리</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>FastAPI</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>의존성 방향</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>API·서비스·저장소·도메인·ML 추론 계층을 분리하고 의존성 방향을 단방향으로 유지한다.</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>100건 x 10회 반복 테스트에서 점수 편차 0.</t>
-        </is>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>아키텍처 다이어그램과 패키지 구조로 증빙.</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K86" s="5" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="20" t="inlineStr">
-        <is>
-          <t>NFR-ML-006</t>
-        </is>
-      </c>
-      <c r="B87" s="21" t="inlineStr">
-        <is>
-          <t>모델</t>
-        </is>
-      </c>
-      <c r="C87" s="21" t="inlineStr">
-        <is>
-          <t>재학습</t>
-        </is>
-      </c>
-      <c r="D87" s="21" t="inlineStr">
-        <is>
-          <t>누적 데이터</t>
-        </is>
-      </c>
-      <c r="E87" s="21" t="inlineStr">
-        <is>
-          <t>주기</t>
-        </is>
-      </c>
-      <c r="F87" s="21" t="inlineStr">
-        <is>
-          <t>챌린지 후보로 채택되는 생활습관 피처는 학습 데이터에서 라벨과의 상관관계 또는 유의미한 영향력이 사전에 검증된 것이어야 한다.</t>
-        </is>
-      </c>
-      <c r="G87" s="21" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H87" s="21" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I87" s="21" t="inlineStr">
-        <is>
-          <t>피처별 SHAP 중요도 평균(절댓값) 상위 5위 이내이거나, 라벨과의 상관계수 절댓값이 0.1 이상인 피처만 챌린지 후보로 채택한다. 기준 미달 피처는 챌린지 후보에서 제외하거나 참고용으로만 표시한다. 분석 결과는 REQ-CHAL의 고정·선택 미션 분류 근거로 사용한다.</t>
-        </is>
-      </c>
-      <c r="J87" s="21" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K87" s="21" t="inlineStr">
+      <c r="K87" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -9557,7 +9678,7 @@
     <row r="88" ht="27" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>NFR-ARCH-001</t>
+          <t>NFR-ARCH-002</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -9567,22 +9688,22 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>계층 분리</t>
+          <t>확장성</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>질환·모델</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>의존성 방향</t>
+          <t>인터페이스</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>API·서비스·저장소·도메인·ML 추론 계층을 분리하고 의존성 방향을 단방향으로 유지한다.</t>
+          <t>질환과 모델을 추가할 때 기존 로직 수정 없이 확장할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -9597,7 +9718,7 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>아키텍처 다이어그램과 패키지 구조로 증빙.</t>
+          <t>확장 시나리오 1건을 문서로 제시.</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
@@ -9612,57 +9733,57 @@
       </c>
     </row>
     <row r="89" ht="27" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>NFR-ARCH-002</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>NFR-ARCH-003</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>아키텍처</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>확장성</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>질환·모델</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>인터페이스</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>질환과 모델을 추가할 때 기존 로직 수정 없이 확장할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>A · B 분리</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>독립 배포</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>모델 A와 모델 B를 각각 독립적으로 교체·배포할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H89" s="9" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>확장 시나리오 1건을 문서로 제시.</t>
-        </is>
-      </c>
-      <c r="J89" s="5" t="inlineStr">
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>모델별 버전과 추론 경로를 분리한다. 한쪽 교체가 다른 쪽 결과에 영향을 주지 않음을 확인한다.</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K89" s="5" t="inlineStr">
+      <c r="K89" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -9671,7 +9792,7 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>NFR-ARCH-003</t>
+          <t>NFR-ARCH-004</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -9681,22 +9802,22 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>모델</t>
+          <t>비교</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>A · B 분리</t>
+          <t>모델 버전</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>독립 배포</t>
+          <t>고정</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>모델 A와 모델 B를 각각 독립적으로 교체·배포할 수 있어야 한다.</t>
+          <t>전·후 비교는 동일한 모델 버전으로 계산해야 하며, 모든 예측 결과에 사용한 모델 버전을 함께 저장한다.</t>
         </is>
       </c>
       <c r="G90" s="9" t="inlineStr">
@@ -9711,12 +9832,12 @@
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
-          <t>모델별 버전과 추론 경로를 분리한다. 한쪽 교체가 다른 쪽 결과에 영향을 주지 않음을 확인한다.</t>
+          <t>비교 대상 두 결과의 모델 버전이 다르면 비교를 표시하지 않고 안내 문구로 대체한다.</t>
         </is>
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>W11 추이 · 변화 추적</t>
         </is>
       </c>
       <c r="K90" s="9" t="inlineStr">
@@ -9728,7 +9849,7 @@
     <row r="91" ht="27" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
         <is>
-          <t>NFR-ARCH-004</t>
+          <t>NFR-ARCH-005</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -9738,22 +9859,22 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>비교</t>
+          <t>설정</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>모델 버전</t>
+          <t>챌린지·설문</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>고정</t>
+          <t>데이터 주도</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>전·후 비교는 동일한 모델 버전으로 계산해야 하며, 모든 예측 결과에 사용한 모델 버전을 함께 저장한다.</t>
+          <t>챌린지 카테고리·미션과 설문 문항은 코드 수정 없이 데이터로 추가·변경할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G91" s="9" t="inlineStr">
@@ -9763,17 +9884,17 @@
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>중간</t>
         </is>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>비교 대상 두 결과의 모델 버전이 다르면 비교를 표시하지 않고 안내 문구로 대체한다.</t>
+          <t>미션 1건 추가가 배포 없이 반영되는 것을 시연.</t>
         </is>
       </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>W11 추이 · 변화 추적</t>
+          <t>해당 없음</t>
         </is>
       </c>
       <c r="K91" s="9" t="inlineStr">
@@ -9783,57 +9904,57 @@
       </c>
     </row>
     <row r="92" ht="27" customHeight="1">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>NFR-ARCH-005</t>
-        </is>
-      </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>아키텍처</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>챌린지·설문</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>데이터 주도</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>챌린지 카테고리·미션과 설문 문항은 코드 수정 없이 데이터로 추가·변경할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G92" s="9" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>NFR-OPS-001</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>상태 점검</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>서비스</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>헬스 체크</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>배포된 서비스는 상태 점검 엔드포인트를 제공해야 한다.</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H92" s="9" t="inlineStr">
+      <c r="H92" s="5" t="inlineStr">
         <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="I92" s="9" t="inlineStr">
-        <is>
-          <t>미션 1건 추가가 배포 없이 반영되는 것을 시연.</t>
-        </is>
-      </c>
-      <c r="J92" s="9" t="inlineStr">
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>GET /health 200. DB·큐 연결 상태 포함.</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K92" s="9" t="inlineStr">
+      <c r="K92" s="5" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -9842,7 +9963,7 @@
     <row r="93" ht="27" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>NFR-OPS-001</t>
+          <t>NFR-OPS-002</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -9852,22 +9973,22 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>상태 점검</t>
+          <t>오류 추적</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>요청</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>헬스 체크</t>
+          <t>추적 ID</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>배포된 서비스는 상태 점검 엔드포인트를 제공해야 한다.</t>
+          <t>모든 요청에 추적 ID를 부여하고 오류 로그에 포함해야 한다.</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -9882,7 +10003,7 @@
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>GET /health 200. DB·큐 연결 상태 포함.</t>
+          <t>오류 응답과 로그에서 동일 추적 ID로 연결 가능.</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
@@ -9899,7 +10020,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>NFR-OPS-002</t>
+          <t>NFR-OPS-003</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
@@ -9909,22 +10030,22 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>오류 추적</t>
+          <t>배포</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>요청</t>
+          <t>재현성</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>추적 ID</t>
+          <t>Docker·환경변수</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>모든 요청에 추적 ID를 부여하고 오류 로그에 포함해야 한다.</t>
+          <t>배포는 Docker로 재현 가능해야 하며 비밀값은 환경변수로 주입한다.</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -9934,305 +10055,305 @@
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>코드에 API 키·모델명 하드코딩 금지. .env.example 제공.</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>NFR-OPS-004</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>변경 이력</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>모델 버전과 계수 변경 이력을 기록하고 조회할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
           <t>중간</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>오류 응답과 로그에서 동일 추적 ID로 연결 가능.</t>
-        </is>
-      </c>
-      <c r="J94" s="5" t="inlineStr">
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>변경 일시·변경자·사유를 기록. 과거 예측 결과에서 사용 버전을 역추적 가능.</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K94" s="5" t="inlineStr">
+      <c r="K95" s="9" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>NFR-OPS-003</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
+    <row r="96" ht="27" customHeight="1">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>NFR-OPS-005</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>운영</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>배포</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>재현성</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>Docker·환경변수</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>배포는 Docker로 재현 가능해야 하며 비밀값은 환경변수로 주입한다.</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>배치</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>재평가</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>리마인더 발송</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>사이클 종료 시점의 중간 재평가 안내와 3~6개월 주기의 전체 재검진 안내를 각각 자동으로 발송해야 한다.</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr">
         <is>
           <t>비기능</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="H96" s="11" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>두 주기의 스케줄을 분리해 관리한다. 작업 실패 시 재시도와 알림(REQ-NOTI-001 연계).</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K96" s="11" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="27" customHeight="1">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>NFR-OPS-006</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>모니터링</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>인식 실패</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>지표 수집</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>검진 결과지 인식 실패율을 지표로 수집해야 한다.</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>실패율이 임계치를 넘으면 직접 입력 안내를 우선 노출하도록 전환.</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>W04 건강정보 입력</t>
+        </is>
+      </c>
+      <c r="K97" s="9" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="27" customHeight="1">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>NFR-ML-009</t>
+        </is>
+      </c>
+      <c r="B98" s="16" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="C98" s="16" t="inlineStr">
+        <is>
+          <t>재학습</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="inlineStr">
+        <is>
+          <t>누적 데이터</t>
+        </is>
+      </c>
+      <c r="E98" s="16" t="inlineStr">
+        <is>
+          <t>주기</t>
+        </is>
+      </c>
+      <c r="F98" s="16" t="inlineStr">
+        <is>
+          <t>챌린지 수행으로 쌓인 측정·생활습관 데이터를 모델 재학습에 반영할 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G98" s="16" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H98" s="16" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>재학습 주기와 데이터 범위를 문서로 정의한다. 재학습 후 성능 지표를 비교해 기록한다.</t>
+        </is>
+      </c>
+      <c r="J98" s="16" t="inlineStr">
+        <is>
+          <t>해당 없음</t>
+        </is>
+      </c>
+      <c r="K98" s="16" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="inlineStr">
+        <is>
+          <t>NFR-ML-007</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>데이터셋</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>모델 이원화</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
+        <is>
+          <t>독립 학습</t>
+        </is>
+      </c>
+      <c r="F99" s="14" t="inlineStr">
+        <is>
+          <t>모델 A(장기 위험)와 모델 B(현재 위험)는 서로 다른 데이터셋으로 각각 독립적으로 학습하며, 두 데이터를 하나로 합쳐 학습하지 않는다.</t>
+        </is>
+      </c>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>비기능</t>
+        </is>
+      </c>
+      <c r="H99" s="14" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>코드에 API 키·모델명 하드코딩 금지. .env.example 제공.</t>
-        </is>
-      </c>
-      <c r="J95" s="5" t="inlineStr">
+      <c r="I99" s="14" t="inlineStr">
+        <is>
+          <t>모델 A는 Framingham Heart Study(미국, 코호트, 10년 후 CHD 예측), 모델 B는 국민건강영양조사 2022-2024(한국, 횡단면, 현재 경계군 여부 예측) 데이터셋을 사용한다. 두 모델의 학습 코드·아티팩트(모델 파일·스케일러)는 분리해 관리한다.</t>
+        </is>
+      </c>
+      <c r="J99" s="14" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="K95" s="5" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="27" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>NFR-OPS-004</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>모델</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>변경 이력</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>기록</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>모델 버전과 계수 변경 이력을 기록하고 조회할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H96" s="9" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>변경 일시·변경자·사유를 기록. 과거 예측 결과에서 사용 버전을 역추적 가능.</t>
-        </is>
-      </c>
-      <c r="J96" s="9" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K96" s="9" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="27" customHeight="1">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>NFR-OPS-005</t>
-        </is>
-      </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="C97" s="11" t="inlineStr">
-        <is>
-          <t>배치</t>
-        </is>
-      </c>
-      <c r="D97" s="11" t="inlineStr">
-        <is>
-          <t>재평가</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>리마인더 발송</t>
-        </is>
-      </c>
-      <c r="F97" s="11" t="inlineStr">
-        <is>
-          <t>사이클 종료 시점의 중간 재평가 안내와 3~6개월 주기의 전체 재검진 안내를 각각 자동으로 발송해야 한다.</t>
-        </is>
-      </c>
-      <c r="G97" s="11" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H97" s="11" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I97" s="11" t="inlineStr">
-        <is>
-          <t>두 주기의 스케줄을 분리해 관리한다. 작업 실패 시 재시도와 알림(REQ-NOTI-001 연계).</t>
-        </is>
-      </c>
-      <c r="J97" s="11" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K97" s="11" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="27" customHeight="1">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>NFR-OPS-006</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>운영</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>모니터링</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>인식 실패</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>지표 수집</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>검진 결과지 인식 실패율을 지표로 수집해야 한다.</t>
-        </is>
-      </c>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H98" s="9" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>실패율이 임계치를 넘으면 직접 입력 안내를 우선 노출하도록 전환.</t>
-        </is>
-      </c>
-      <c r="J98" s="9" t="inlineStr">
-        <is>
-          <t>W04 건강정보 입력</t>
-        </is>
-      </c>
-      <c r="K98" s="9" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="15" t="inlineStr">
-        <is>
-          <t>NFR-ML-009</t>
-        </is>
-      </c>
-      <c r="B99" s="16" t="inlineStr">
-        <is>
-          <t>모델</t>
-        </is>
-      </c>
-      <c r="C99" s="16" t="inlineStr">
-        <is>
-          <t>재학습</t>
-        </is>
-      </c>
-      <c r="D99" s="16" t="inlineStr">
-        <is>
-          <t>누적 데이터</t>
-        </is>
-      </c>
-      <c r="E99" s="16" t="inlineStr">
-        <is>
-          <t>주기</t>
-        </is>
-      </c>
-      <c r="F99" s="16" t="inlineStr">
-        <is>
-          <t>챌린지 수행으로 쌓인 측정·생활습관 데이터를 모델 재학습에 반영할 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G99" s="16" t="inlineStr">
-        <is>
-          <t>비기능</t>
-        </is>
-      </c>
-      <c r="H99" s="16" t="inlineStr">
-        <is>
-          <t>중간</t>
-        </is>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
-        <is>
-          <t>재학습 주기와 데이터 범위를 문서로 정의한다. 재학습 후 성능 지표를 비교해 기록한다.</t>
-        </is>
-      </c>
-      <c r="J99" s="16" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-      <c r="K99" s="16" t="inlineStr">
+      <c r="K99" s="14" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -10241,7 +10362,7 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>NFR-ML-007</t>
+          <t>NFR-ML-008</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
@@ -10251,22 +10372,22 @@
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>데이터셋</t>
+          <t>모집단</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>모델 이원화</t>
+          <t>학습 대상</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>독립 학습</t>
+          <t>고혈압군 제외</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>모델 A(장기 위험)와 모델 B(현재 위험)는 서로 다른 데이터셋으로 각각 독립적으로 학습하며, 두 데이터를 하나로 합쳐 학습하지 않는다.</t>
+          <t>모델 B의 학습 데이터 모집단은 정상 또는 경계군에 해당하는 응답자로 한정하며, 이미 고혈압(4단계)에 해당하는 응답자는 학습 대상에서 제외한다.</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
@@ -10281,7 +10402,7 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>모델 A는 Framingham Heart Study(미국, 코호트, 10년 후 CHD 예측), 모델 B는 국민건강영양조사 2022-2024(한국, 횡단면, 현재 경계군 여부 예측) 데이터셋을 사용한다. 두 모델의 학습 코드·아티팩트(모델 파일·스케일러)는 분리해 관리한다.</t>
+          <t>HE_HP=1(정상), 2·3(경계군)에 해당하는 응답자만 학습에 포함하고, HE_HP=4(고혈압)는 제외한다. 이는 학습 데이터 구성 단계의 필터링이며, 서비스 시점의 사용자 자격 판단(REQ-ELIG-002, 자기보고 기반)과는 별개 기준이다.</t>
         </is>
       </c>
       <c r="J100" s="14" t="inlineStr">
@@ -10298,37 +10419,37 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>NFR-ML-008</t>
+          <t>REQ-PRED-008</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>모델</t>
+          <t>예측·분석</t>
         </is>
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>모집단</t>
+          <t>결과 입력</t>
         </is>
       </c>
       <c r="D101" s="14" t="inlineStr">
         <is>
-          <t>학습 대상</t>
+          <t>나트륨 설문</t>
         </is>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>고혈압군 제외</t>
+          <t>점수화</t>
         </is>
       </c>
       <c r="F101" s="14" t="inlineStr">
         <is>
-          <t>모델 B의 학습 데이터 모집단은 정상 또는 경계군에 해당하는 응답자로 한정하며, 이미 고혈압(4단계)에 해당하는 응답자는 학습 대상에서 제외한다.</t>
+          <t>사용자는 나트륨 섭취 수준을 5문항 설문으로 응답하고, 그 응답이 점수화·등급화되어 모델 B의 나트륨 섭취 피처로 반영되어야 한다.</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
         <is>
-          <t>비기능</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="H101" s="14" t="inlineStr">
@@ -10338,12 +10459,12 @@
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
-          <t>HE_HP=1(정상), 2·3(경계군)에 해당하는 응답자만 학습에 포함하고, HE_HP=4(고혈압)는 제외한다. 이는 학습 데이터 구성 단계의 필터링이며, 서비스 시점의 사용자 자격 판단(REQ-ELIG-002, 자기보고 기반)과는 별개 기준이다.</t>
+          <t>5개 문항(국물·김치·면류·절임·양념) 각 0~2점, 합산 0~10점. 0~3점=하(≤2,088mg), 4~6점=중(2,088~3,363mg), 7~10점=상(&gt;3,363mg)으로 매핑해 모델 B 입력값으로 사용한다. 등급 컷은 KNHANES 2022-2024 병합 데이터의 나트륨 섭취량 실측 삼분위수 기준이다.</t>
         </is>
       </c>
       <c r="J101" s="14" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>W04 건강정보 입력</t>
         </is>
       </c>
       <c r="K101" s="14" t="inlineStr">
@@ -10353,228 +10474,114 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="13" t="inlineStr">
-        <is>
-          <t>REQ-PRED-008</t>
-        </is>
-      </c>
-      <c r="B102" s="14" t="inlineStr">
+      <c r="A102" s="26" t="inlineStr">
+        <is>
+          <t>REQ-PRED-009</t>
+        </is>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
         <is>
           <t>예측·분석</t>
         </is>
       </c>
-      <c r="C102" s="14" t="inlineStr">
-        <is>
-          <t>결과 입력</t>
-        </is>
-      </c>
-      <c r="D102" s="14" t="inlineStr">
-        <is>
-          <t>나트륨 설문</t>
-        </is>
-      </c>
-      <c r="E102" s="14" t="inlineStr">
-        <is>
-          <t>점수화</t>
-        </is>
-      </c>
-      <c r="F102" s="14" t="inlineStr">
-        <is>
-          <t>사용자는 나트륨 섭취 수준을 5문항 설문으로 응답하고, 그 응답이 점수화·등급화되어 모델 B의 나트륨 섭취 피처로 반영되어야 한다.</t>
-        </is>
-      </c>
-      <c r="G102" s="14" t="inlineStr">
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>위험 예측</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="inlineStr">
+        <is>
+          <t>대상군 정의</t>
+        </is>
+      </c>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t>경계군 분류</t>
+        </is>
+      </c>
+      <c r="F102" s="17" t="inlineStr">
+        <is>
+          <t>모델 B의 라벨은 정상(0) vs 경계군(1, 주의혈압·고혈압전단계)의 이진 분류로 정의한다. 학습 데이터 모집단 구성은 NFR-ML-007을 따른다.</t>
+        </is>
+      </c>
+      <c r="G102" s="17" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H102" s="14" t="inlineStr">
+      <c r="H102" s="17" t="inlineStr">
         <is>
           <t>높음</t>
         </is>
       </c>
-      <c r="I102" s="14" t="inlineStr">
-        <is>
-          <t>5개 문항(국물·김치·면류·절임·양념) 각 0~2점, 합산 0~10점. 0~3점=하(≤2,088mg), 4~6점=중(2,088~3,363mg), 7~10점=상(&gt;3,363mg)으로 매핑해 모델 B 입력값으로 사용한다. 등급 컷은 KNHANES 2022-2024 병합 데이터의 나트륨 섭취량 실측 삼분위수 기준이다.</t>
-        </is>
-      </c>
-      <c r="J102" s="14" t="inlineStr">
-        <is>
-          <t>W04 건강정보 입력</t>
-        </is>
-      </c>
-      <c r="K102" s="14" t="inlineStr">
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>라벨은 정상(0)/경계군(1) 이진값으로 정의한다. 서비스에서 예측 제공 대상자 판단은 REQ-ELIG-002(자기보고 기반 기진단 여부)를 그대로 따르며, 사용자가 입력한 혈압 수치가 고혈압 기준에 해당하더라도 자기보고상 미진단이면 예측을 제공하고 결과가 위험 단계이면 REQ-PRED-005(검사·상담 안내)로 연결한다. (참고: 학습 데이터에서 HE_HP=4(고혈압) 응답자를 제외하는 것은 훈련 모집단 구성의 문제이며, REQ-ELIG-002의 서비스 시점 자기보고 기준과는 별개다 — NFR-ML-007 참고)</t>
+        </is>
+      </c>
+      <c r="J102" s="17" t="inlineStr">
+        <is>
+          <t>W06 예측 결과 · XAI 설명</t>
+        </is>
+      </c>
+      <c r="K102" s="17" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="26" t="inlineStr">
-        <is>
-          <t>REQ-PRED-009</t>
-        </is>
-      </c>
-      <c r="B103" s="17" t="inlineStr">
-        <is>
-          <t>예측·분석</t>
-        </is>
-      </c>
-      <c r="C103" s="17" t="inlineStr">
-        <is>
-          <t>위험 예측</t>
-        </is>
-      </c>
-      <c r="D103" s="17" t="inlineStr">
-        <is>
-          <t>대상군 정의</t>
-        </is>
-      </c>
-      <c r="E103" s="17" t="inlineStr">
-        <is>
-          <t>경계군 분류</t>
-        </is>
-      </c>
-      <c r="F103" s="17" t="inlineStr">
-        <is>
-          <t>모델 B의 라벨은 정상(0) vs 경계군(1, 주의혈압·고혈압전단계)의 이진 분류로 정의한다. 학습 데이터 모집단 구성은 NFR-ML-007을 따른다.</t>
-        </is>
-      </c>
-      <c r="G103" s="17" t="inlineStr">
+      <c r="A103" s="13" t="inlineStr">
+        <is>
+          <t>REQ-NOTI-002</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>리마인더</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="inlineStr">
+        <is>
+          <t>건강정보 입력</t>
+        </is>
+      </c>
+      <c r="E103" s="14" t="inlineStr">
+        <is>
+          <t>발송</t>
+        </is>
+      </c>
+      <c r="F103" s="14" t="inlineStr">
+        <is>
+          <t>사용자는 건강정보 재입력(재검진) 시점에 알림을 받을 수 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="G103" s="14" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="H103" s="17" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="I103" s="17" t="inlineStr">
-        <is>
-          <t>라벨은 정상(0)/경계군(1) 이진값으로 정의한다. 서비스에서 예측 제공 대상자 판단은 REQ-ELIG-002(자기보고 기반 기진단 여부)를 그대로 따르며, 사용자가 입력한 혈압 수치가 고혈압 기준에 해당하더라도 자기보고상 미진단이면 예측을 제공하고 결과가 위험 단계이면 REQ-PRED-005(검사·상담 안내)로 연결한다. (참고: 학습 데이터에서 HE_HP=4(고혈압) 응답자를 제외하는 것은 훈련 모집단 구성의 문제이며, REQ-ELIG-002의 서비스 시점 자기보고 기준과는 별개다 — NFR-ML-007 참고)</t>
-        </is>
-      </c>
-      <c r="J103" s="17" t="inlineStr">
-        <is>
-          <t>W06 예측 결과 · XAI 설명</t>
-        </is>
-      </c>
-      <c r="K103" s="17" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="13" t="inlineStr">
-        <is>
-          <t>REQ-NOTI-002</t>
-        </is>
-      </c>
-      <c r="B104" s="14" t="inlineStr">
-        <is>
-          <t>알림</t>
-        </is>
-      </c>
-      <c r="C104" s="14" t="inlineStr">
-        <is>
-          <t>리마인더</t>
-        </is>
-      </c>
-      <c r="D104" s="14" t="inlineStr">
-        <is>
-          <t>건강정보 입력</t>
-        </is>
-      </c>
-      <c r="E104" s="14" t="inlineStr">
-        <is>
-          <t>발송</t>
-        </is>
-      </c>
-      <c r="F104" s="14" t="inlineStr">
-        <is>
-          <t>사용자는 건강정보 재입력(재검진) 시점에 알림을 받을 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G104" s="14" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H104" s="14" t="inlineStr">
+      <c r="H103" s="14" t="inlineStr">
         <is>
           <t>낮음</t>
         </is>
       </c>
-      <c r="I104" s="14" t="inlineStr">
+      <c r="I103" s="14" t="inlineStr">
         <is>
           <t>사용자별 알림 수신 설정을 따르며 미설정 시 발송하지 않는다.</t>
         </is>
       </c>
-      <c r="J104" s="14" t="inlineStr">
+      <c r="J103" s="14" t="inlineStr">
         <is>
           <t>W12 피드백 · 마이페이지</t>
         </is>
       </c>
-      <c r="K104" s="14" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="13" t="inlineStr">
-        <is>
-          <t>REQ-NOTI-003</t>
-        </is>
-      </c>
-      <c r="B105" s="14" t="inlineStr">
-        <is>
-          <t>알림</t>
-        </is>
-      </c>
-      <c r="C105" s="14" t="inlineStr">
-        <is>
-          <t>리마인더</t>
-        </is>
-      </c>
-      <c r="D105" s="14" t="inlineStr">
-        <is>
-          <t>예방행동가이드 확인</t>
-        </is>
-      </c>
-      <c r="E105" s="14" t="inlineStr">
-        <is>
-          <t>발송</t>
-        </is>
-      </c>
-      <c r="F105" s="14" t="inlineStr">
-        <is>
-          <t>사용자는 새로 생성된 예방 행동 제안(LLM 추천)을 확인하라는 알림을 받을 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G105" s="14" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H105" s="14" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-      <c r="I105" s="14" t="inlineStr">
-        <is>
-          <t>사용자별 알림 수신 설정을 따르며 미설정 시 발송하지 않는다.</t>
-        </is>
-      </c>
-      <c r="J105" s="14" t="inlineStr">
-        <is>
-          <t>W12 피드백 · 마이페이지</t>
-        </is>
-      </c>
-      <c r="K105" s="14" t="inlineStr">
+      <c r="K103" s="14" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -12944,12 +12951,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>위험 범주 표시, 주요 기여 요인 목록(방향·중요도), 면책 문구, 예방 행동 제안</t>
+          <t>위험 범주 표시, 주요 기여 요인 목록(방향·중요도), 면책 문구</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>REQ-PRED-001, REQ-PRED-003, REQ-PRED-006, REQ-RECO-001, NFR-SAFE-001, NFR-SAFE-002, NFR-SAFE-003, NFR-SAFE-005, NFR-SAFE-007</t>
+          <t>REQ-PRED-001, REQ-PRED-003, REQ-PRED-006,  NFR-SAFE-001, NFR-SAFE-002, NFR-SAFE-003, NFR-SAFE-005, NFR-SAFE-007</t>
         </is>
       </c>
     </row>

--- a/docs/요구사항_정의서_파이온_최종.xlsx
+++ b/docs/요구사항_정의서_파이온_최종.xlsx
@@ -19,12 +19,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보류 · 결정 필요" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'요구사항 정의서'!$A$1:$K$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'요구사항 정의서'!$A$1:$K$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'문서 대조'!$A$1:$E$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'미션 카탈로그'!$A$1:$H$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'지표 · 이벤트'!$A$1:$H$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'화면 흐름'!$A$1:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'화면 목록'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'화면 목록'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="152511" fullCalcOnLoad="1"/>
 </workbook>
@@ -1233,7 +1233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1872,6 +1872,43 @@
       <c r="G18" s="27" t="inlineStr">
         <is>
           <t>식단 사진 분석(REQ-RECO-002)은 추천이 아니라 분석이라 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>v1.8</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>화면 목록에 삭제된 REQ-CHAL-011 참조 · W08 "하단 탭" · 설문·4주 재평가 결과 화면 W-ID 없음, W11이 두 뜻으로 사용됨 · 복약·측정이 "기본 보완" 미션으로 남아 3개 미션 구성과 충돌</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>W09에서 REQ-CHAL-011 제거, W08 상단 네비게이션으로 수정, 화면 목록에 W04-2(생활습관 설문)·W11-2(4주 전·후 비교) 추가 및 화면 흐름 시트에 W-ID 병기, 관련 화면 ID(HEALTH-005·008, PRED-008) 정정 / REQ-HEALTH-002 선택 항목에 공복혈당 명시(개정 v0.3 내용이 본문에서 빠져 있었음) / W04-2 설문에서 흡연·음주 문항 제외(W04 건강정보 입력에서 수집) / REQ-HEALTH-002 음주 빈도를 필수 항목으로 변경, REQ-CHAL-008 판정 기준을 건강정보 입력으로 정정(설문 → 건강정보 입력), 미션 카탈로그 흡연·음주 행 정정 / 혈압 측정을 미션에서 빼 주 1회 상시 기록으로 확정(미션 카탈로그 복약·측정 행) / 응급 문진 양성 시 REQ-ELIG-003·NFR-SAFE-004을 "안내 후 그래도 진행 확인 버튼" 방식으로 통일 / 모델 B 제외(모델 A 단독, 10년 관상동맥질환 예측): REQ-PRED-001·006·008, REQ-ELIG-002, REQ-HEALTH-002·008, NFR-ML-006·007, NFR-ARCH-003 수정, NFR-ML-008·REQ-PRED-009 삭제 / 고혈압 진단 여부와 혈압약 복용을 "고혈압 진단·치료 상태" 질문 하나로 통합</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>문서 충돌 체크리스트 반영 — 와이어프레임 v4와 화면 ID·용어 통일</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="inlineStr">
+        <is>
+          <t>통합</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>나이 제한: 가입은 허용하고 범위 밖은 위험 예측만 제외, 챌린지 참여 가능(REQ-ELIG-001 그대로). 응급 시 진행 여부(ELIG-003 vs NFR-SAFE-004)는 보류 / 음주 빈도 필수 결정: 비흡연·비음주는 나트륨 미션으로 대체하는 판정이 W04 입력에 기대므로 / 응급 진행 여부와 혈압 측정 포함 여부 확정(9/28 팀 결정) / 고혈압 진단자도 예측 대상(입력으로 사용). 심혈관질환 진단자 제외 범위·서비스 대상 질환 표현은 팀 확인 필요</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.00500011" customWidth="1" min="1" max="1"/>
@@ -4686,6 +4723,330 @@
         </is>
       </c>
       <c r="F88" s="27" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="27" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+      <c r="B89" s="27" t="inlineStr">
+        <is>
+          <t>NFR-ML-008</t>
+        </is>
+      </c>
+      <c r="C89" s="27" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D89" s="27" t="inlineStr">
+        <is>
+          <t>모델 B 학습 모집단(고혈압군 제외) 정의</t>
+        </is>
+      </c>
+      <c r="E89" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 모델 B 제외, 모델 A 단독</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="27" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+      <c r="B90" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-009</t>
+        </is>
+      </c>
+      <c r="C90" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D90" s="27" t="inlineStr">
+        <is>
+          <t>모델 B 라벨(정상 vs 경계군) 정의</t>
+        </is>
+      </c>
+      <c r="E90" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 모델 B 제외, 모델 A 단독</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-001</t>
+        </is>
+      </c>
+      <c r="C91" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D91" s="27" t="inlineStr">
+        <is>
+          <t>모델 A(10년 관상동맥질환) 단독 예측으로 변경</t>
+        </is>
+      </c>
+      <c r="E91" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 모델 B 제외(모델 A 단독)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-006</t>
+        </is>
+      </c>
+      <c r="C92" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="inlineStr">
+        <is>
+          <t>카드 2개를 10년 위험 · 혈관 나이로 재정의</t>
+        </is>
+      </c>
+      <c r="E92" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 모델 B 제외(모델 A 단독)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B93" s="27" t="inlineStr">
+        <is>
+          <t>REQ-PRED-008</t>
+        </is>
+      </c>
+      <c r="C93" s="27" t="inlineStr">
+        <is>
+          <t>예측·분석</t>
+        </is>
+      </c>
+      <c r="D93" s="27" t="inlineStr">
+        <is>
+          <t>나트륨 점수를 모델 입력이 아닌 챌린지 후보 판정용으로 변경</t>
+        </is>
+      </c>
+      <c r="E93" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 모델 B 제외(모델 A 단독)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B94" s="27" t="inlineStr">
+        <is>
+          <t>NFR-ML-006</t>
+        </is>
+      </c>
+      <c r="C94" s="27" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D94" s="27" t="inlineStr">
+        <is>
+          <t>챌린지 피처 채택 기준을 모델 A 수정 가능 요인 기준으로 변경</t>
+        </is>
+      </c>
+      <c r="E94" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 모델 B 제외(모델 A 단독)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>NFR-ML-007</t>
+        </is>
+      </c>
+      <c r="C95" s="27" t="inlineStr">
+        <is>
+          <t>모델</t>
+        </is>
+      </c>
+      <c r="D95" s="27" t="inlineStr">
+        <is>
+          <t>모델 이원화 → 모델 A 단독</t>
+        </is>
+      </c>
+      <c r="E95" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 모델 B 제외(모델 A 단독)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>NFR-ARCH-003</t>
+        </is>
+      </c>
+      <c r="C96" s="27" t="inlineStr">
+        <is>
+          <t>아키텍처</t>
+        </is>
+      </c>
+      <c r="D96" s="27" t="inlineStr">
+        <is>
+          <t>A·B 분리 → 모델 버전 단위 교체</t>
+        </is>
+      </c>
+      <c r="E96" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 모델 B 제외(모델 A 단독)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B97" s="27" t="inlineStr">
+        <is>
+          <t>REQ-ELIG-002</t>
+        </is>
+      </c>
+      <c r="C97" s="27" t="inlineStr">
+        <is>
+          <t>이용 적합성</t>
+        </is>
+      </c>
+      <c r="D97" s="27" t="inlineStr">
+        <is>
+          <t>고혈압 진단자는 제외하지 않고 입력으로 사용</t>
+        </is>
+      </c>
+      <c r="E97" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 모델 B 제외(모델 A 단독)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B98" s="27" t="inlineStr">
+        <is>
+          <t>REQ-HEALTH-002</t>
+        </is>
+      </c>
+      <c r="C98" s="27" t="inlineStr">
+        <is>
+          <t>건강정보</t>
+        </is>
+      </c>
+      <c r="D98" s="27" t="inlineStr">
+        <is>
+          <t>필수 항목에 고혈압 진단·치료 상태·총콜레스테롤·HDL 추가</t>
+        </is>
+      </c>
+      <c r="E98" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 모델 B 제외(모델 A 단독)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B99" s="27" t="inlineStr">
+        <is>
+          <t>REQ-HEALTH-008</t>
+        </is>
+      </c>
+      <c r="C99" s="27" t="inlineStr">
+        <is>
+          <t>건강정보</t>
+        </is>
+      </c>
+      <c r="D99" s="27" t="inlineStr">
+        <is>
+          <t>4주 재입력 항목을 모델 A 입력 기준으로 변경</t>
+        </is>
+      </c>
+      <c r="E99" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 모델 B 제외(모델 A 단독)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="27" t="inlineStr">
+        <is>
+          <t>수정</t>
+        </is>
+      </c>
+      <c r="B100" s="27" t="inlineStr">
+        <is>
+          <t>REQ-CHAL-008</t>
+        </is>
+      </c>
+      <c r="C100" s="27" t="inlineStr">
+        <is>
+          <t>챌린지</t>
+        </is>
+      </c>
+      <c r="D100" s="27" t="inlineStr">
+        <is>
+          <t>고정 칸 대체 판정 기준을 설문에서 건강정보 입력으로 변경</t>
+        </is>
+      </c>
+      <c r="E100" s="27" t="inlineStr">
+        <is>
+          <t>팀 결정 — 흡연·음주를 건강정보에서 수집</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4699,7 +5060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.00500011" customWidth="1" min="1" max="1"/>
@@ -5257,7 +5618,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>대상 질환을 이미 진단받은 사용자는 신규 위험 예측 대상에서 제외하고 생활습관 기능과 의료기관 안내로 연결해야 한다.</t>
+          <t>대상 질환(관상동맥질환)을 이미 진단받은 사용자는 신규 위험 예측 대상에서 제외하고 생활습관 기능과 의료기관 안내로 연결해야 한다. 고혈압 진단·치료 상태는 제외 조건이 아니라 예측 입력으로 사용한다.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -5272,7 +5633,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>기진단자에게 위험 확률을 생성·표시하지 않는다. 챌린지·대시보드는 계속 이용 가능.</t>
+          <t>기진단자에게 위험 확률을 생성·표시하지 않는다. 챌린지·대시보드는 계속 이용 가능. 고혈압 진단자와 혈압약 복용자는 예측 대상이며 고혈압 진단·치료 상태는 모델 입력으로 수집한다. (심혈관질환 진단자 제외 범위는 모델 문서의 적용 대상 정의 확인 후 확정)</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -5329,7 +5690,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>119 전화를 원터치로 제공. 이후 화면 진행을 차단하지 않되 안내를 상단 고정.</t>
+          <t>119 전화를 원터치로 제공. "예" 또는 "잘 모르겠습니다"를 선택하면 안내를 상단에 고정하고, "그래도 진행하시겠습니까?" 확인 버튼을 눌러야 다음 화면으로 진행한다.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -5485,7 +5846,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>사용자는 위험 예측 모델에 필요한 건강정보를 입력할 수 있어야 한다. 필수 항목은 수축기혈압·이완기혈압·신장·체중·흡연 여부·당뇨병 여부·부모 고혈압 가족력이며, 선택 항목은 총콜레스테롤·HDL콜레스테롤·음주 빈도·운동 빈도이다. 나이·성별은 REQ-HEALTH-001의 프로필 정보를 그대로 참조한다.</t>
+          <t>사용자는 위험 예측 모델에 필요한 건강정보를 입력할 수 있어야 한다. 필수 항목은 수축기혈압·이완기혈압·신장·체중·흡연 여부·음주 빈도·당뇨병 여부·고혈압 진단·치료 상태(진단 없음 / 진단받았지만 약은 안 먹음 / 진단받았고 약을 먹는 중)·총콜레스테롤·HDL콜레스테롤·부모 고혈압 가족력이며, 선택 항목은 공복혈당·운동 빈도이다. 나이·성별은 REQ-HEALTH-001의 프로필 정보를 그대로 참조한다.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -5676,7 +6037,7 @@
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t>W04 건강정보 입력</t>
+          <t>W04-2 생활습관 설문</t>
         </is>
       </c>
       <c r="K17" s="19" t="inlineStr">
@@ -5842,12 +6203,12 @@
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>4주 재입력 항목은 모델 B 입력과 일치해야 한다. 전체 재입력 전에는 혈당·콜레스테롤을 직전 값으로 유지하고 그 사실을 화면에 표시한다.</t>
+          <t>4주 재입력 항목은 모델 A 입력 중 4주 사이 바뀔 수 있는 항목(혈압·흡연 상태 등)과 일치해야 한다. 전체 재입력 전에는 혈당·콜레스테롤을 직전 값으로 유지하고 그 사실을 화면에 표시한다.</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>W04 건강정보 입력</t>
+          <t>W04 건강정보 입력 · W11-2 4주 전·후 비교</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
@@ -5874,7 +6235,7 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>두 모델</t>
+          <t>단일 모델</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -5884,7 +6245,7 @@
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>사용자는 두 가지 모델의 결과를 함께 확인할 수 있어야 한다. 모델 A는 10년 후 고혈압 발생 가능성, 모델 B는 현재 시점의 경계군 해당 여부를 제시한다.</t>
+          <t>사용자는 모델 A의 결과로 10년 내 관상동맥질환 발병 위험을 확인할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -5899,7 +6260,7 @@
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>결과는 진단이 아닌 선별 정보. 위험 범주는 정상·경계·위험 3단계로 하고 색상(초록·노랑·빨강)과 텍스트를 함께 표시한다. 정상은 추가 안내 없음, 경계는 기여 요인과 챌린지를 함께 제시, 위험은 REQ-PRED-005(검사·상담 안내)로 연결한다. 두 모델의 결과를 하나로 합산하지 않는다.</t>
+          <t>결과는 진단이 아닌 선별 정보. 위험 범주는 정상·경계·위험 3단계로 하고 색상(초록·노랑·빨강)과 텍스트를 함께 표시한다. 구간 기준은 모델 문서에 따른다. 정상은 추가 안내 없음, 경계는 기여 요인과 챌린지를 함께 제시, 위험은 REQ-PRED-005(검사·상담 안내)로 연결한다.</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -6164,12 +6525,12 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>장기 · 현재 분리</t>
+          <t>위험 · 혈관 나이</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>예측 결과는 카드 2개로 나누어 제시한다. 첫 번째 카드는 장기 위험(혈관 나이 · 실제 나이 비교), 두 번째 카드는 현재 식습관 위험 신호와 그에 연결된 챌린지 추천 근거를 담는다.</t>
+          <t>예측 결과는 카드 2개로 나누어 제시한다. 첫 번째 카드는 10년 내 관상동맥질환 발병 위험과 위험 구간, 두 번째 카드는 혈관 나이와 실제 나이 비교를 담는다.</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -6184,7 +6545,7 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>두 카드를 하나의 종합 점수로 합치지 않는다. 혈관 나이는 추정치임을 함께 표기하고 NFR-SAFE-001을 따른다.</t>
+          <t>혈관 나이는 추정치임을 함께 표기하고 NFR-SAFE-001을 따른다.</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -6697,7 +7058,7 @@
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>설문에서 비흡연·비음주로 판정되면 해당 고정 칸을 나트륨 미션으로 채운다. 나트륨도 이미 낮으면 기여도가 가장 큰 개선 가능 요인으로 대체한다.</t>
+          <t>건강정보 입력(흡연 여부·음주 빈도)에서 비흡연·비음주로 판정되면 해당 고정 칸을 나트륨 미션으로 채운다. 나트륨도 이미 낮으면 기여도가 가장 큰 개선 가능 요인으로 대체한다.</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
@@ -8122,7 +8483,7 @@
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>응급 문진 양성 시 입력·예측 화면 진입을 막고 안내만 노출(REQ-ELIG-003 연계).</t>
+          <t>응급 문진 양성("예" 또는 "잘 모르겠습니다") 시 응급 연락 안내를 먼저 노출하고, "그래도 진행" 확인 전에는 입력·예측 화면에 들어가지 않는다(REQ-ELIG-003 연계).</t>
         </is>
       </c>
       <c r="J60" s="9" t="inlineStr">
@@ -9589,7 +9950,7 @@
       </c>
       <c r="F86" s="21" t="inlineStr">
         <is>
-          <t>챌린지 후보로 채택되는 생활습관 피처는 학습 데이터에서 라벨과의 상관관계 또는 유의미한 영향력이 사전에 검증된 것이어야 한다.</t>
+          <t>챌린지 후보로 채택되는 생활습관 항목은 모델 A에서 바꿀 수 있는 위험 요인(수축기혈압·콜레스테롤 등)과 연결되는 것이어야 한다.</t>
         </is>
       </c>
       <c r="G86" s="21" t="inlineStr">
@@ -9604,7 +9965,7 @@
       </c>
       <c r="I86" s="21" t="inlineStr">
         <is>
-          <t>피처별 SHAP 중요도 평균(절댓값) 상위 5위 이내이거나, 라벨과의 상관계수 절댓값이 0.1 이상인 피처만 챌린지 후보로 채택한다. 기준 미달 피처는 챌린지 후보에서 제외하거나 참고용으로만 표시한다. 분석 결과는 REQ-CHAL의 고정·선택 미션 분류 근거로 사용한다.</t>
+          <t>모델 A의 수정 가능 요인(SHAP 중요도 상위 5위 이내)과 연결되는 챌린지를 후보로 채택한다. 연결 근거가 없는 항목은 후보에서 제외하거나 참고용으로만 표시한다. 분석 결과는 REQ-CHAL의 고정·선택 미션 분류 근거로 사용한다.</t>
         </is>
       </c>
       <c r="J86" s="21" t="inlineStr">
@@ -9750,7 +10111,7 @@
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>A · B 분리</t>
+          <t>모델 교체</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -9760,7 +10121,7 @@
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>모델 A와 모델 B를 각각 독립적으로 교체·배포할 수 있어야 한다.</t>
+          <t>예측 모델은 버전 단위로 독립적으로 교체·배포할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G89" s="9" t="inlineStr">
@@ -9775,7 +10136,7 @@
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>모델별 버전과 추론 경로를 분리한다. 한쪽 교체가 다른 쪽 결과에 영향을 주지 않음을 확인한다.</t>
+          <t>모델별 버전과 추론 경로를 분리한다. 모델 교체가 챌린지 추천·대시보드 결과에 영향을 주지 않음을 확인한다.</t>
         </is>
       </c>
       <c r="J89" s="9" t="inlineStr">
@@ -10320,17 +10681,17 @@
       </c>
       <c r="D99" s="14" t="inlineStr">
         <is>
-          <t>모델 이원화</t>
+          <t>단일 모델</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>독립 학습</t>
+          <t>학습 데이터</t>
         </is>
       </c>
       <c r="F99" s="14" t="inlineStr">
         <is>
-          <t>모델 A(장기 위험)와 모델 B(현재 위험)는 서로 다른 데이터셋으로 각각 독립적으로 학습하며, 두 데이터를 하나로 합쳐 학습하지 않는다.</t>
+          <t>예측 모델은 모델 A(10년 관상동맥질환 예측) 하나만 사용한다. 모델 B(현재 경계군 분류)는 사용하지 않는다.</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">
@@ -10345,7 +10706,7 @@
       </c>
       <c r="I99" s="14" t="inlineStr">
         <is>
-          <t>모델 A는 Framingham Heart Study(미국, 코호트, 10년 후 CHD 예측), 모델 B는 국민건강영양조사 2022-2024(한국, 횡단면, 현재 경계군 여부 예측) 데이터셋을 사용한다. 두 모델의 학습 코드·아티팩트(모델 파일·스케일러)는 분리해 관리한다.</t>
+          <t>모델 A는 Framingham Heart Study(미국, 코호트, 10년 후 CHD 예측) 데이터셋을 사용한다. 학습 코드·아티팩트(모델 파일·스케일러)는 버전별로 분리해 관리한다.</t>
         </is>
       </c>
       <c r="J99" s="14" t="inlineStr">
@@ -10362,37 +10723,37 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>NFR-ML-008</t>
+          <t>REQ-PRED-008</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>모델</t>
+          <t>예측·분석</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>모집단</t>
+          <t>결과 입력</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>학습 대상</t>
+          <t>나트륨 설문</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>고혈압군 제외</t>
+          <t>점수화</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>모델 B의 학습 데이터 모집단은 정상 또는 경계군에 해당하는 응답자로 한정하며, 이미 고혈압(4단계)에 해당하는 응답자는 학습 대상에서 제외한다.</t>
+          <t>사용자는 나트륨 섭취 수준을 5문항 설문으로 응답하고, 그 응답이 점수화·등급화되어 챌린지 추천·제외 판단(나트륨 미션 후보)에 반영되어야 한다.</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
         <is>
-          <t>비기능</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="H100" s="14" t="inlineStr">
@@ -10402,12 +10763,12 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>HE_HP=1(정상), 2·3(경계군)에 해당하는 응답자만 학습에 포함하고, HE_HP=4(고혈압)는 제외한다. 이는 학습 데이터 구성 단계의 필터링이며, 서비스 시점의 사용자 자격 판단(REQ-ELIG-002, 자기보고 기반)과는 별개 기준이다.</t>
+          <t>5개 문항(국물·김치·면류·절임·양념) 각 0~2점, 합산 0~10점. 0~3점=하(≤2,088mg), 4~6점=중(2,088~3,363mg), 7~10점=상(&gt;3,363mg)으로 매핑해 챌린지 후보 판정에 사용한다(예측 모델 입력이 아님). 등급 컷은 KNHANES 2022-2024 병합 데이터의 나트륨 섭취량 실측 삼분위수 기준이다.</t>
         </is>
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>W04-2 생활습관 설문</t>
         </is>
       </c>
       <c r="K100" s="14" t="inlineStr">
@@ -10419,32 +10780,32 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>REQ-PRED-008</t>
+          <t>REQ-NOTI-002</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>예측·분석</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>결과 입력</t>
+          <t>리마인더</t>
         </is>
       </c>
       <c r="D101" s="14" t="inlineStr">
         <is>
-          <t>나트륨 설문</t>
+          <t>건강정보 입력</t>
         </is>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>점수화</t>
+          <t>발송</t>
         </is>
       </c>
       <c r="F101" s="14" t="inlineStr">
         <is>
-          <t>사용자는 나트륨 섭취 수준을 5문항 설문으로 응답하고, 그 응답이 점수화·등급화되어 모델 B의 나트륨 섭취 피처로 반영되어야 한다.</t>
+          <t>사용자는 건강정보 재입력(재검진) 시점에 알림을 받을 수 있어야 한다.</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
@@ -10454,17 +10815,17 @@
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음</t>
         </is>
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
-          <t>5개 문항(국물·김치·면류·절임·양념) 각 0~2점, 합산 0~10점. 0~3점=하(≤2,088mg), 4~6점=중(2,088~3,363mg), 7~10점=상(&gt;3,363mg)으로 매핑해 모델 B 입력값으로 사용한다. 등급 컷은 KNHANES 2022-2024 병합 데이터의 나트륨 섭취량 실측 삼분위수 기준이다.</t>
+          <t>사용자별 알림 수신 설정을 따르며 미설정 시 발송하지 않는다.</t>
         </is>
       </c>
       <c r="J101" s="14" t="inlineStr">
         <is>
-          <t>W04 건강정보 입력</t>
+          <t>W12 피드백 · 마이페이지</t>
         </is>
       </c>
       <c r="K101" s="14" t="inlineStr">
@@ -10473,122 +10834,8 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="26" t="inlineStr">
-        <is>
-          <t>REQ-PRED-009</t>
-        </is>
-      </c>
-      <c r="B102" s="17" t="inlineStr">
-        <is>
-          <t>예측·분석</t>
-        </is>
-      </c>
-      <c r="C102" s="17" t="inlineStr">
-        <is>
-          <t>위험 예측</t>
-        </is>
-      </c>
-      <c r="D102" s="17" t="inlineStr">
-        <is>
-          <t>대상군 정의</t>
-        </is>
-      </c>
-      <c r="E102" s="17" t="inlineStr">
-        <is>
-          <t>경계군 분류</t>
-        </is>
-      </c>
-      <c r="F102" s="17" t="inlineStr">
-        <is>
-          <t>모델 B의 라벨은 정상(0) vs 경계군(1, 주의혈압·고혈압전단계)의 이진 분류로 정의한다. 학습 데이터 모집단 구성은 NFR-ML-007을 따른다.</t>
-        </is>
-      </c>
-      <c r="G102" s="17" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H102" s="17" t="inlineStr">
-        <is>
-          <t>높음</t>
-        </is>
-      </c>
-      <c r="I102" s="17" t="inlineStr">
-        <is>
-          <t>라벨은 정상(0)/경계군(1) 이진값으로 정의한다. 서비스에서 예측 제공 대상자 판단은 REQ-ELIG-002(자기보고 기반 기진단 여부)를 그대로 따르며, 사용자가 입력한 혈압 수치가 고혈압 기준에 해당하더라도 자기보고상 미진단이면 예측을 제공하고 결과가 위험 단계이면 REQ-PRED-005(검사·상담 안내)로 연결한다. (참고: 학습 데이터에서 HE_HP=4(고혈압) 응답자를 제외하는 것은 훈련 모집단 구성의 문제이며, REQ-ELIG-002의 서비스 시점 자기보고 기준과는 별개다 — NFR-ML-007 참고)</t>
-        </is>
-      </c>
-      <c r="J102" s="17" t="inlineStr">
-        <is>
-          <t>W06 예측 결과 · XAI 설명</t>
-        </is>
-      </c>
-      <c r="K102" s="17" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="13" t="inlineStr">
-        <is>
-          <t>REQ-NOTI-002</t>
-        </is>
-      </c>
-      <c r="B103" s="14" t="inlineStr">
-        <is>
-          <t>알림</t>
-        </is>
-      </c>
-      <c r="C103" s="14" t="inlineStr">
-        <is>
-          <t>리마인더</t>
-        </is>
-      </c>
-      <c r="D103" s="14" t="inlineStr">
-        <is>
-          <t>건강정보 입력</t>
-        </is>
-      </c>
-      <c r="E103" s="14" t="inlineStr">
-        <is>
-          <t>발송</t>
-        </is>
-      </c>
-      <c r="F103" s="14" t="inlineStr">
-        <is>
-          <t>사용자는 건강정보 재입력(재검진) 시점에 알림을 받을 수 있어야 한다.</t>
-        </is>
-      </c>
-      <c r="G103" s="14" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="H103" s="14" t="inlineStr">
-        <is>
-          <t>낮음</t>
-        </is>
-      </c>
-      <c r="I103" s="14" t="inlineStr">
-        <is>
-          <t>사용자별 알림 수신 설정을 따르며 미설정 시 발송하지 않는다.</t>
-        </is>
-      </c>
-      <c r="J103" s="14" t="inlineStr">
-        <is>
-          <t>W12 피드백 · 마이페이지</t>
-        </is>
-      </c>
-      <c r="K103" s="14" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K99"/>
+  <autoFilter ref="A1:K101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
@@ -10957,7 +11204,7 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>나트륨 5문항 점수화 — 설문 문항 규칙이 여기 종속</t>
+          <t>나트륨 5문항 점수화 — 챌린지 후보 판정용(모델 입력 아님)</t>
         </is>
       </c>
     </row>
@@ -10979,12 +11226,12 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>삭제</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>모델 B 라벨 정의와 학습 모집단</t>
+          <t>모델 B 제외(팀 결정)로 삭제</t>
         </is>
       </c>
     </row>
@@ -11147,12 +11394,12 @@
       </c>
       <c r="B4" s="25" t="inlineStr">
         <is>
-          <t>흡연 여부, 음주 빈도·양, 폭음</t>
+          <t>흡연 여부, 음주 빈도 (건강정보 입력에서 수집, 둘 다 필수)</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>비흡연·비음주면 후속 문항 및 해당 미션 제외</t>
+          <t>비흡연이면 금연 칸, 비음주면 절주 칸을 나트륨 미션으로 대체</t>
         </is>
       </c>
       <c r="D4" s="25" t="inlineStr">
@@ -11278,17 +11525,17 @@
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>측정 수단이 있으면 기록 미션 제안</t>
+          <t>측정 수단이 있으면 주 1회 혈압 기록 안내</t>
         </is>
       </c>
       <c r="D7" s="25" t="inlineStr">
         <is>
-          <t>주 1회 같은 시간 혈압 측정</t>
+          <t>주 1회 같은 시간 혈압 기록</t>
         </is>
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>기본 보완</t>
+          <t>상시 기록 (3개 미션에 포함하지 않음)</t>
         </is>
       </c>
       <c r="F7" s="25" t="inlineStr">
@@ -12370,7 +12617,7 @@
     <row r="2">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>초기 설문</t>
+          <t>초기 설문 W04-2</t>
         </is>
       </c>
       <c r="B2" s="25" t="inlineStr">
@@ -12407,7 +12654,7 @@
     <row r="3">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>추천 결과</t>
+          <t>추천 결과 W09(상단)</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -12555,7 +12802,7 @@
     <row r="7">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>결과 W11</t>
+          <t>결과 W11-2</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
@@ -12762,7 +13009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.005000109999999" customWidth="1" min="1" max="1"/>
@@ -12897,233 +13144,287 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>기본 정보, 계측·혈압, 생활습관, 가족력, 필드 오류 표시, 검진 이력 추가</t>
+          <t>기본 정보, 계측·혈압, 가족력, 검진 결과지 사진 채우기, 필드 오류 표시, 검진 이력 추가</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-001, REQ-HEALTH-002, REQ-HEALTH-003, REQ-HEALTH-004, REQ-HEALTH-005, REQ-HEALTH-006, REQ-HEALTH-008, NFR-SEC-003, NFR-SEC-005, NFR-SEC-006, NFR-SEC-007, NFR-OPS-006</t>
+          <t>REQ-HEALTH-001, REQ-HEALTH-002, REQ-HEALTH-003, REQ-HEALTH-004, REQ-HEALTH-006, REQ-HEALTH-008, NFR-SEC-003, NFR-SEC-005, NFR-SEC-006, NFR-SEC-007, NFR-OPS-006</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>W05</t>
+          <t>W04-2</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>입력 검토 · 분석 대기</t>
+          <t>생활습관 설문</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>확인 → 비동기 분석</t>
+          <t>선택지 응답 → 조건부 건너뛰기 → 다음</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>입력값 검토 요약, 분석 요청 버튼, 대기·실행·완료·실패·재시도 상태</t>
+          <t>단계 표시(7단계), 선택형 문항, 운동 종목 선택·강도 자동 분류, 조건부 문항 건너뛰기, 이전·다음</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>REQ-HEALTH-007, REQ-PRED-002, NFR-ASYNC-001</t>
+          <t>REQ-HEALTH-005, REQ-PRED-008, REQ-CHAL-001, REQ-CHAL-008</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>W06</t>
+          <t>W05</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>예측 결과 · XAI 설명</t>
+          <t>입력 검토 · 분석 대기</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>선별 결과 → 설명 → 다음 행동</t>
+          <t>확인 → 비동기 분석</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>위험 범주 표시, 주요 기여 요인 목록(방향·중요도), 면책 문구</t>
+          <t>입력값 검토 요약, 분석 요청 버튼, 대기·실행·완료·실패·재시도 상태</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>REQ-PRED-001, REQ-PRED-003, REQ-PRED-006,  NFR-SAFE-001, NFR-SAFE-002, NFR-SAFE-003, NFR-SAFE-005, NFR-SAFE-007</t>
+          <t>REQ-HEALTH-007, REQ-PRED-002, NFR-ASYNC-001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>W07</t>
+          <t>W06</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>검사 · 상담 안내</t>
+          <t>예측 결과 · XAI 설명</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>고위험 → 의료기관</t>
+          <t>선별 결과 → 설명 → 다음 행동</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>고위험 안내 문구, 검사 권고, 의료기관 정보, 면책 문구</t>
+          <t>위험 범주 표시, 주요 기여 요인 목록(방향·중요도), 면책 문구</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>REQ-PRED-005, NFR-SAFE-001</t>
+          <t>REQ-PRED-001, REQ-PRED-003, REQ-PRED-006,  NFR-SAFE-001, NFR-SAFE-002, NFR-SAFE-003, NFR-SAFE-005, NFR-SAFE-007</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>W08</t>
+          <t>W07</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>대시보드 (홈)</t>
+          <t>검사 · 상담 안내</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>상태 요약 → 오늘의 실천</t>
+          <t>고위험 → 의료기관</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>하단 탭, 최신 위험도 카드, 오늘의 챌린지 진행률, 사이클 현황, 빈 상태 CTA</t>
+          <t>고위험 안내 문구, 검사 권고, 의료기관 정보, 면책 문구</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>REQ-PRED-004, REQ-PRED-007, REQ-DASH-001, REQ-DASH-004, REQ-DASH-005, REQ-DASH-006, REQ-DASH-007, REQ-DASH-008, REQ-DASH-009, REQ-DASH-010, REQ-DASH-011, NFR-DASH-001, NFR-SAFE-001, NFR-SAFE-005</t>
+          <t>REQ-PRED-005, NFR-SAFE-001</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>W09</t>
+          <t>W08</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>챌린지 선택</t>
+          <t>대시보드 (홈)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>추천 → 선택 → 시작</t>
+          <t>상태 요약 → 오늘의 실천</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>예측 근거별 챌린지 후보, 연결된 위험 요인 표시, 목표 횟수 설정, 사이클 시작</t>
+          <t>상단 네비게이션, 최신 위험도 카드, 오늘의 챌린지 진행률, 사이클 현황, 빈 상태 CTA</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>REQ-CHAL-001, REQ-CHAL-002, REQ-CHAL-003, REQ-CHAL-008, REQ-CHAL-009, REQ-CHAL-011, NFR-DASH-001, REQ-FEED-003, NFR-SAFE-007</t>
+          <t>REQ-PRED-004, REQ-PRED-007, REQ-DASH-001, REQ-DASH-004, REQ-DASH-005, REQ-DASH-006, REQ-DASH-007, REQ-DASH-008, REQ-DASH-009, REQ-DASH-010, REQ-DASH-011, NFR-DASH-001, NFR-SAFE-001, NFR-SAFE-005</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W09</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>챌린지 수행 · 인증</t>
+          <t>챌린지 선택</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>목표 → 인증 → 달성률</t>
+          <t>추천 → 선택 → 시작</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>오늘의 목표 목록, 인증하기, 당일 기록 수정, 주간·사이클 달성률, 식단 사진 업로드</t>
+          <t>예측 근거별 챌린지 후보, 연결된 위험 요인 표시, 목표 횟수 설정, 사이클 시작, 고정 미션 2개, 제외한 챌린지·이유</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>REQ-CHAL-004, REQ-CHAL-005, REQ-CHAL-006, REQ-CHAL-007, REQ-CHAL-010, REQ-DASH-008, REQ-DASH-009, NFR-DASH-001, REQ-RECO-002</t>
+          <t>REQ-CHAL-001, REQ-CHAL-002, REQ-CHAL-003, REQ-CHAL-008, REQ-CHAL-009, NFR-DASH-001, REQ-FEED-003, NFR-SAFE-007</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>추이 · 변화 추적</t>
+          <t>챌린지 수행 · 인증</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>이력 → 차트</t>
+          <t>목표 → 인증 → 달성률</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>예측 이력 차트, 최초 대비 증감(색상+기호), 기간 필터, 데이터 1건 이하 빈 상태</t>
+          <t>오늘의 목표 목록, 인증하기, 당일 기록 수정, 주간·사이클 달성률, 식단 사진 업로드</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>REQ-DASH-002, REQ-DASH-003, REQ-DASH-010, REQ-FEED-002, NFR-SAFE-005, NFR-ARCH-004</t>
+          <t>REQ-CHAL-004, REQ-CHAL-005, REQ-CHAL-006, REQ-CHAL-007, REQ-CHAL-010, REQ-DASH-008, REQ-DASH-009, NFR-DASH-001, REQ-RECO-002</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>추이 · 변화 추적</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>이력 → 차트</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>예측 이력 차트, 최초 대비 증감(색상+기호), 기간 필터, 데이터 1건 이하 빈 상태</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>REQ-DASH-002, REQ-DASH-003, REQ-DASH-010, REQ-FEED-002, NFR-SAFE-005, NFR-ARCH-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>W11-2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>4주 전 · 후 비교</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>재입력 → 같은 모델 → 변화</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>시작·4주 후 위험도 비교, 혈관 나이 변화, 혈압 추이, 순위 변화 한 줄 해석, 다음 4주 챌린지 선택</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>REQ-HEALTH-008, REQ-PRED-007, REQ-DASH-003, REQ-DASH-011</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>피드백 · 마이페이지</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>의견 → 저장 / 계정 관리</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>결과·추천 평가와 의견 입력, 알림 수신 설정, 동의 철회, 회원 탈퇴</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>REQ-USER-003, REQ-CONSENT-002, REQ-NOTI-001, REQ-FEED-001</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
